--- a/sources/2A_Manha_2_Bimestre.xlsx
+++ b/sources/2A_Manha_2_Bimestre.xlsx
@@ -61,7 +61,7 @@
     <x:t>Conselho Segundo Bimestre</x:t>
   </x:si>
   <x:si>
-    <x:t>277</x:t>
+    <x:t>334</x:t>
   </x:si>
   <x:si>
     <x:t>0 (Soma de todas as eletivas)</x:t>
@@ -198,15 +198,18 @@
     <x:t>2</x:t>
   </x:si>
   <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
     <x:t>5</x:t>
   </x:si>
   <x:si>
     <x:t>3</x:t>
   </x:si>
   <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
     <x:t>4</x:t>
   </x:si>
   <x:si>
@@ -219,175 +222,256 @@
     <x:t>1</x:t>
   </x:si>
   <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
     <x:t>7</x:t>
   </x:si>
   <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALESSANDRO DE OLIVEIRA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>82%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALEX EDUARDO GALLO FERREIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>77%</x:t>
+  </x:si>
+  <x:si>
     <x:t>79%</x:t>
   </x:si>
   <x:si>
+    <x:t>ALEXANDRE DIAS FREITAS JUNIOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Baixa - Transferência</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMANDA LIZZE SOUZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>68%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRUNO HENRIQUE VILARES MORCELLI DE CASTRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CARLOS EDUARDO PAZ BEZERRA DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DANIELLY SAMYRA ANDRADES DE FRANÇA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>87%</x:t>
+  </x:si>
+  <x:si>
     <x:t>88%</x:t>
   </x:si>
   <x:si>
-    <x:t>ALESSANDRO DE OLIVEIRA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
+    <x:t>DIOGO JANUARIO DIAS DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDUARDO ROBERTO FERREIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELIPE FONTINHAS DE MIRANDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>80%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>84%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GABRIEL FERREIRA DE CARVALHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>92%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GABRIEL MARQUES DANTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GABRIEL NICACIO MENEZES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME EVANGELISTA LIMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME OLIVEIRA DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME RIBEIRO DE LIMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME SILVA MEIRA RAMOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME VICTOR SILVA DA CRUZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME VINHAS SILVA FARIAS DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUSTAVO DA SILVA OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>97%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HENRIQUE BARAUNA DO CARMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRID GABRIELLY QUEIROZ DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISABELLA FERNANDES DIAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISRAEL ALVES SARAIVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOAO VICTOR BATISTA CITRANGULO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>59%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JULIA FORTUNATO RODRIGUES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JULIO CÉSAR GONÇALVES SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREN MAYSA CONDORI MAYTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAUAN DOS SANTOS SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Remanejamento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KEVIN OLIVEIRA MENDES ARAUJO</x:t>
   </x:si>
   <x:si>
     <x:t>83%</x:t>
   </x:si>
   <x:si>
-    <x:t>87%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALEX EDUARDO GALLO FERREIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>80%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALEXANDRE DIAS FREITAS JUNIOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Baixa - Transferência</x:t>
-  </x:si>
-  <x:si>
-    <x:t>93%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMANDA LIZZE SOUZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>72%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>77%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRUNO HENRIQUE VILARES MORCELLI DE CASTRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CARLOS EDUARDO PAZ BEZERRA DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>64%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>74%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DANIELLY SAMYRA ANDRADES DE FRANÇA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>89%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIOGO JANUARIO DIAS DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDUARDO ROBERTO FERREIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELIPE FONTINHAS DE MIRANDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>86%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GABRIEL FERREIRA DE CARVALHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>92%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GABRIEL MARQUES DANTAS</x:t>
+    <x:t>LEONARDO DE SOUZA ARAUJO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUCAS MASSI AGUENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANUELLA MARTINS KRAUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARIA CLARA DAMASIO ZANINI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARIA EDUARDA PONCIANO DOS SANTOS</x:t>
   </x:si>
   <x:si>
     <x:t>96%</x:t>
   </x:si>
   <x:si>
-    <x:t>GABRIEL NICACIO MENEZES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>98%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME EVANGELISTA LIMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>73%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME OLIVEIRA DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>84%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME RIBEIRO DE LIMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME SILVA MEIRA RAMOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME VICTOR SILVA DA CRUZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME VINHAS SILVA FARIAS DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUSTAVO DA SILVA OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>97%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HENRIQUE BARAUNA DO CARMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRID GABRIELLY QUEIROZ DE OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISABELLA FERNANDES DIAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISRAEL ALVES SARAIVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOAO VICTOR BATISTA CITRANGULO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27</x:t>
+    <x:t>MARIA VITÓRIA RODRIGUES DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEDRO HENRIQUE SOUZA BOMBARDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEDRO HENRIQUE SOUZA MENDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEDRO RIBEIRO FERNANDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIETRO TEIXEIRA DE MOURA MENDONCA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAFAEL MARQUES DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAFAEL SANTANA DE AVEIRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
   </x:si>
   <x:si>
     <x:t>60%</x:t>
@@ -396,81 +480,6 @@
     <x:t>70%</x:t>
   </x:si>
   <x:si>
-    <x:t>JULIA FORTUNATO RODRIGUES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JULIO CÉSAR GONÇALVES SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREN MAYSA CONDORI MAYTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAUAN DOS SANTOS SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Remanejamento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>94%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KEVIN OLIVEIRA MENDES ARAUJO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LEONARDO DE SOUZA ARAUJO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUCAS MASSI AGUENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANUELLA MARTINS KRAUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIA CLARA DAMASIO ZANINI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIA EDUARDA PONCIANO DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIA VITÓRIA RODRIGUES DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEDRO HENRIQUE SOUZA BOMBARDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEDRO HENRIQUE SOUZA MENDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEDRO RIBEIRO FERNANDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIETRO TEIXEIRA DE MOURA MENDONCA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>81%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAFAEL MARQUES DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAFAEL SANTANA DE AVEIRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>71%</x:t>
-  </x:si>
-  <x:si>
     <x:t>RAFAELA SANTIAGO DE MORAES</x:t>
   </x:si>
   <x:si>
@@ -507,13 +516,16 @@
     <x:t>GUILHERME FELIX RIBEIRO MONTEIRO</x:t>
   </x:si>
   <x:si>
+    <x:t>78%</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve"> </x:t>
   </x:si>
   <x:si>
     <x:t>Aulas Dadas: 22</x:t>
   </x:si>
   <x:si>
-    <x:t>Aulas Dadas: 0</x:t>
+    <x:t>Aulas Dadas: 29</x:t>
   </x:si>
   <x:si>
     <x:t>Aulas Dadas: 11</x:t>
@@ -1482,10 +1494,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I13" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J13" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K13" s="12">
         <x:v>1</x:v>
@@ -1614,10 +1626,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA13" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB13" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC13" s="12">
         <x:v>1</x:v>
@@ -1667,22 +1679,22 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="L14" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M14" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N14" s="12" t="s">
         <x:v>49</x:v>
@@ -1691,7 +1703,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="P14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q14" s="12" t="s">
         <x:v>49</x:v>
@@ -1715,10 +1727,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="X14" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="Y14" s="12" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="Y14" s="12" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="Z14" s="12" t="s">
         <x:v>49</x:v>
@@ -1727,10 +1739,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AB14" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC14" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD14" s="12" t="s">
         <x:v>49</x:v>
@@ -1739,10 +1751,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AF14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG14" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AH14" s="12" t="s">
         <x:v>49</x:v>
@@ -1751,10 +1763,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AJ14" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK14" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL14" s="12" t="s">
         <x:v>49</x:v>
@@ -1763,13 +1775,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AN14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO14" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="AP14" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AQ14" s="12">
         <x:v>2</x:v>
@@ -1778,7 +1790,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AS14" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT14" s="12" t="s">
         <x:v>49</x:v>
@@ -1790,7 +1802,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AW14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX14" s="12" t="s">
         <x:v>49</x:v>
@@ -1799,42 +1811,42 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AZ14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BA14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="BD14" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BE14" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BF14" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BG14" s="12">
-        <x:v>57</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="BH14" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="BI14" s="12">
-        <x:v>72</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BJ14" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:62">
       <x:c r="A15" s="11" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B15" s="12" t="s">
         <x:v>53</x:v>
@@ -1846,7 +1858,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E15" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F15" s="12" t="s">
         <x:v>49</x:v>
@@ -1855,22 +1867,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="L15" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M15" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N15" s="12" t="s">
         <x:v>49</x:v>
@@ -1891,10 +1903,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="T15" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U15" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="V15" s="12" t="s">
         <x:v>49</x:v>
@@ -1903,10 +1915,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="X15" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y15" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Z15" s="12" t="s">
         <x:v>49</x:v>
@@ -1915,10 +1927,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AB15" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC15" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD15" s="12" t="s">
         <x:v>49</x:v>
@@ -1927,10 +1939,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AF15" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG15" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH15" s="12" t="s">
         <x:v>49</x:v>
@@ -1942,7 +1954,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK15" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AL15" s="12" t="s">
         <x:v>49</x:v>
@@ -1951,10 +1963,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AN15" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AO15" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AP15" s="12" t="s">
         <x:v>49</x:v>
@@ -1963,10 +1975,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AR15" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS15" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AT15" s="12" t="s">
         <x:v>49</x:v>
@@ -1987,19 +1999,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AZ15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BB15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="BD15" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE15" s="12" t="s">
         <x:v>55</x:v>
@@ -2008,16 +2020,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG15" s="12">
-        <x:v>46</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BH15" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BI15" s="12">
-        <x:v>79</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="BJ15" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:62">
@@ -2031,7 +2043,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D16" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E16" s="12" t="s">
         <x:v>55</x:v>
@@ -2043,13 +2055,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K16" s="12">
         <x:v>4</x:v>
@@ -2070,7 +2082,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="Q16" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="R16" s="12" t="s">
         <x:v>49</x:v>
@@ -2079,7 +2091,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="T16" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U16" s="12" t="s">
         <x:v>55</x:v>
@@ -2091,10 +2103,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="X16" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Y16" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Z16" s="12" t="s">
         <x:v>49</x:v>
@@ -2106,7 +2118,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AC16" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD16" s="12" t="s">
         <x:v>49</x:v>
@@ -2115,10 +2127,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AF16" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG16" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH16" s="12" t="s">
         <x:v>49</x:v>
@@ -2130,7 +2142,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK16" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AL16" s="12" t="s">
         <x:v>49</x:v>
@@ -2142,7 +2154,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AO16" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AP16" s="12" t="s">
         <x:v>49</x:v>
@@ -2151,10 +2163,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AR16" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS16" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AT16" s="12" t="s">
         <x:v>49</x:v>
@@ -2175,34 +2187,34 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AZ16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC16" s="12">
         <x:v>4</x:v>
       </x:c>
       <x:c r="BD16" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE16" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BF16" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG16" s="12">
-        <x:v>55</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BH16" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BI16" s="12">
-        <x:v>124</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="BJ16" s="12" t="s">
         <x:v>73</x:v>
@@ -2234,10 +2246,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I17" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J17" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K17" s="12">
         <x:v>5</x:v>
@@ -2366,10 +2378,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA17" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB17" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC17" s="12">
         <x:v>5</x:v>
@@ -2419,22 +2431,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="H18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="L18" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M18" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N18" s="12" t="s">
         <x:v>49</x:v>
@@ -2455,10 +2467,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="T18" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="U18" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="V18" s="12" t="s">
         <x:v>49</x:v>
@@ -2470,7 +2482,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="Y18" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Z18" s="12" t="s">
         <x:v>49</x:v>
@@ -2479,7 +2491,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AB18" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC18" s="12" t="s">
         <x:v>55</x:v>
@@ -2491,10 +2503,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AF18" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG18" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AH18" s="12" t="s">
         <x:v>49</x:v>
@@ -2503,10 +2515,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AJ18" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AK18" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AL18" s="12" t="s">
         <x:v>49</x:v>
@@ -2518,7 +2530,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AO18" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP18" s="12" t="s">
         <x:v>78</x:v>
@@ -2527,7 +2539,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AR18" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS18" s="12" t="s">
         <x:v>79</x:v>
@@ -2539,10 +2551,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AV18" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AW18" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AX18" s="12" t="s">
         <x:v>49</x:v>
@@ -2551,13 +2563,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AZ18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BB18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC18" s="12">
         <x:v>6</x:v>
@@ -2572,13 +2584,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG18" s="12">
-        <x:v>78</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="BH18" s="12" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="BI18" s="12">
-        <x:v>145</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="BJ18" s="12" t="s">
         <x:v>81</x:v>
@@ -2610,10 +2622,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K19" s="12">
         <x:v>7</x:v>
@@ -2742,10 +2754,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC19" s="12">
         <x:v>7</x:v>
@@ -2795,22 +2807,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="L20" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M20" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N20" s="12" t="s">
         <x:v>49</x:v>
@@ -2819,10 +2831,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="P20" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q20" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="R20" s="12" t="s">
         <x:v>49</x:v>
@@ -2831,7 +2843,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="T20" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U20" s="12" t="s">
         <x:v>78</x:v>
@@ -2843,10 +2855,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="X20" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y20" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Z20" s="12" t="s">
         <x:v>49</x:v>
@@ -2855,10 +2867,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AB20" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC20" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AD20" s="12" t="s">
         <x:v>49</x:v>
@@ -2867,7 +2879,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AF20" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG20" s="12" t="s">
         <x:v>54</x:v>
@@ -2882,7 +2894,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK20" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="AL20" s="12" t="s">
         <x:v>49</x:v>
@@ -2891,22 +2903,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AN20" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO20" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AP20" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="AQ20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="AR20" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="AS20" s="12" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="AS20" s="12" t="s">
-        <x:v>63</x:v>
       </x:c>
       <x:c r="AT20" s="12" t="s">
         <x:v>49</x:v>
@@ -2915,10 +2927,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AV20" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW20" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX20" s="12" t="s">
         <x:v>49</x:v>
@@ -2927,42 +2939,42 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AZ20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BA20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="BD20" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BE20" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BF20" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG20" s="12">
-        <x:v>101</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="BH20" s="12" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BI20" s="12">
-        <x:v>164</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="BJ20" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:62">
       <x:c r="A21" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B21" s="12" t="s">
         <x:v>53</x:v>
@@ -2971,7 +2983,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D21" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E21" s="12" t="s">
         <x:v>55</x:v>
@@ -2983,19 +2995,19 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="H21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="L21" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M21" s="12" t="s">
         <x:v>55</x:v>
@@ -3007,7 +3019,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="P21" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Q21" s="12" t="s">
         <x:v>55</x:v>
@@ -3031,10 +3043,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="X21" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Y21" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Z21" s="12" t="s">
         <x:v>49</x:v>
@@ -3043,10 +3055,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AB21" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC21" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD21" s="12" t="s">
         <x:v>49</x:v>
@@ -3055,10 +3067,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AF21" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AG21" s="12" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="AG21" s="12" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="AH21" s="12" t="s">
         <x:v>49</x:v>
@@ -3070,7 +3082,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK21" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL21" s="12" t="s">
         <x:v>49</x:v>
@@ -3091,7 +3103,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AR21" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS21" s="12" t="s">
         <x:v>64</x:v>
@@ -3115,42 +3127,42 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AZ21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="BD21" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE21" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF21" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG21" s="12">
-        <x:v>31</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="BH21" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="BI21" s="12">
-        <x:v>64</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="BJ21" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:62">
       <x:c r="A22" s="11" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
         <x:v>75</x:v>
@@ -3174,10 +3186,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K22" s="12">
         <x:v>10</x:v>
@@ -3306,10 +3318,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC22" s="12">
         <x:v>10</x:v>
@@ -3338,7 +3350,7 @@
     </x:row>
     <x:row r="23" spans="1:62">
       <x:c r="A23" s="11" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
         <x:v>53</x:v>
@@ -3347,7 +3359,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D23" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E23" s="12" t="s">
         <x:v>55</x:v>
@@ -3359,22 +3371,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="H23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="L23" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M23" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N23" s="12" t="s">
         <x:v>49</x:v>
@@ -3383,7 +3395,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="P23" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q23" s="12" t="s">
         <x:v>55</x:v>
@@ -3395,10 +3407,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="T23" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U23" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="V23" s="12" t="s">
         <x:v>49</x:v>
@@ -3407,7 +3419,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="X23" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y23" s="12" t="s">
         <x:v>55</x:v>
@@ -3419,7 +3431,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AB23" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC23" s="12" t="s">
         <x:v>49</x:v>
@@ -3443,10 +3455,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AJ23" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK23" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL23" s="12" t="s">
         <x:v>49</x:v>
@@ -3455,7 +3467,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AN23" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO23" s="12" t="s">
         <x:v>55</x:v>
@@ -3479,10 +3491,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AV23" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW23" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AX23" s="12" t="s">
         <x:v>49</x:v>
@@ -3491,42 +3503,42 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AZ23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BA23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BB23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="BD23" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE23" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF23" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG23" s="12">
-        <x:v>36</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BH23" s="12" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="BI23" s="12">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="BI23" s="12">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="BJ23" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:62">
       <x:c r="A24" s="11" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
         <x:v>53</x:v>
@@ -3535,10 +3547,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D24" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E24" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F24" s="12" t="s">
         <x:v>49</x:v>
@@ -3547,22 +3559,22 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="L24" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M24" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N24" s="12" t="s">
         <x:v>49</x:v>
@@ -3577,13 +3589,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="R24" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="S24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="T24" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="U24" s="12" t="s">
         <x:v>55</x:v>
@@ -3595,7 +3607,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="X24" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y24" s="12" t="s">
         <x:v>49</x:v>
@@ -3607,10 +3619,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AB24" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC24" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD24" s="12" t="s">
         <x:v>49</x:v>
@@ -3622,7 +3634,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AG24" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH24" s="12" t="s">
         <x:v>49</x:v>
@@ -3631,10 +3643,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AJ24" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK24" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL24" s="12" t="s">
         <x:v>49</x:v>
@@ -3646,16 +3658,16 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AO24" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AP24" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AQ24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="AR24" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS24" s="12" t="s">
         <x:v>78</x:v>
@@ -3670,7 +3682,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AW24" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AX24" s="12" t="s">
         <x:v>49</x:v>
@@ -3679,42 +3691,42 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AZ24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="BD24" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE24" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BF24" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG24" s="12">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="BH24" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BI24" s="12">
-        <x:v>86</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="BJ24" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:62">
       <x:c r="A25" s="11" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
         <x:v>53</x:v>
@@ -3735,19 +3747,19 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K25" s="12">
         <x:v>13</x:v>
       </x:c>
       <x:c r="L25" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M25" s="12" t="s">
         <x:v>55</x:v>
@@ -3759,7 +3771,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="P25" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q25" s="12" t="s">
         <x:v>55</x:v>
@@ -3771,10 +3783,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="T25" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U25" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="V25" s="12" t="s">
         <x:v>49</x:v>
@@ -3783,7 +3795,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="X25" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y25" s="12" t="s">
         <x:v>49</x:v>
@@ -3795,7 +3807,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AB25" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC25" s="12" t="s">
         <x:v>49</x:v>
@@ -3807,7 +3819,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AF25" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG25" s="12" t="s">
         <x:v>49</x:v>
@@ -3819,10 +3831,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AJ25" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK25" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AL25" s="12" t="s">
         <x:v>49</x:v>
@@ -3843,7 +3855,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AR25" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS25" s="12" t="s">
         <x:v>55</x:v>
@@ -3855,7 +3867,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AV25" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW25" s="12" t="s">
         <x:v>55</x:v>
@@ -3867,13 +3879,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AZ25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BB25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC25" s="12">
         <x:v>13</x:v>
@@ -3882,27 +3894,27 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BE25" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BF25" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG25" s="12">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="BH25" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="BI25" s="12">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="BJ25" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:62">
       <x:c r="A26" s="11" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
         <x:v>53</x:v>
@@ -3923,19 +3935,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="H26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="L26" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M26" s="12" t="s">
         <x:v>49</x:v>
@@ -3959,7 +3971,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="T26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U26" s="12" t="s">
         <x:v>55</x:v>
@@ -3971,7 +3983,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="X26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y26" s="12" t="s">
         <x:v>49</x:v>
@@ -3983,7 +3995,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AB26" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC26" s="12" t="s">
         <x:v>49</x:v>
@@ -3995,10 +4007,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AF26" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG26" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AH26" s="12" t="s">
         <x:v>49</x:v>
@@ -4010,7 +4022,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AL26" s="12" t="s">
         <x:v>49</x:v>
@@ -4025,13 +4037,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AP26" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AQ26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="AR26" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS26" s="12" t="s">
         <x:v>55</x:v>
@@ -4043,10 +4055,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AV26" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW26" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AX26" s="12" t="s">
         <x:v>49</x:v>
@@ -4055,42 +4067,42 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AZ26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BB26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="BD26" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BE26" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BF26" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG26" s="12">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="BH26" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="BI26" s="12">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="BJ26" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:62">
       <x:c r="A27" s="11" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B27" s="12" t="s">
         <x:v>53</x:v>
@@ -4111,22 +4123,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="H27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="L27" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M27" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N27" s="12" t="s">
         <x:v>49</x:v>
@@ -4135,7 +4147,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="P27" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q27" s="12" t="s">
         <x:v>49</x:v>
@@ -4159,7 +4171,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="X27" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y27" s="12" t="s">
         <x:v>49</x:v>
@@ -4171,7 +4183,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AB27" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC27" s="12" t="s">
         <x:v>49</x:v>
@@ -4183,7 +4195,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AF27" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG27" s="12" t="s">
         <x:v>49</x:v>
@@ -4195,10 +4207,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AJ27" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK27" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AL27" s="12" t="s">
         <x:v>49</x:v>
@@ -4207,22 +4219,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AN27" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO27" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP27" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AQ27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="AR27" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS27" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AT27" s="12" t="s">
         <x:v>49</x:v>
@@ -4243,19 +4255,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AZ27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BB27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="BD27" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BE27" s="12" t="s">
         <x:v>49</x:v>
@@ -4264,21 +4276,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG27" s="12">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="BH27" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BI27" s="12">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="BJ27" s="12" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:62">
       <x:c r="A28" s="11" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
         <x:v>75</x:v>
@@ -4302,10 +4314,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K28" s="12">
         <x:v>16</x:v>
@@ -4434,10 +4446,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC28" s="12">
         <x:v>16</x:v>
@@ -4461,12 +4473,12 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="BJ28" s="12" t="s">
-        <x:v>104</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:62">
       <x:c r="A29" s="11" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B29" s="12" t="s">
         <x:v>53</x:v>
@@ -4475,10 +4487,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F29" s="12" t="s">
         <x:v>49</x:v>
@@ -4487,19 +4499,19 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="H29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="L29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M29" s="12" t="s">
         <x:v>55</x:v>
@@ -4511,7 +4523,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q29" s="12" t="s">
         <x:v>55</x:v>
@@ -4523,10 +4535,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="T29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="V29" s="12" t="s">
         <x:v>49</x:v>
@@ -4535,10 +4547,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="X29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y29" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Z29" s="12" t="s">
         <x:v>49</x:v>
@@ -4547,10 +4559,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AB29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC29" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD29" s="12" t="s">
         <x:v>49</x:v>
@@ -4559,7 +4571,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AF29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG29" s="12" t="s">
         <x:v>55</x:v>
@@ -4571,10 +4583,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AJ29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL29" s="12" t="s">
         <x:v>49</x:v>
@@ -4583,7 +4595,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AN29" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AO29" s="12" t="s">
         <x:v>55</x:v>
@@ -4595,10 +4607,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AR29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS29" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AT29" s="12" t="s">
         <x:v>49</x:v>
@@ -4607,10 +4619,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AV29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AX29" s="12" t="s">
         <x:v>49</x:v>
@@ -4619,42 +4631,42 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AZ29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="BB29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="BD29" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BE29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BF29" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG29" s="12">
-        <x:v>43</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BH29" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BI29" s="12">
-        <x:v>81</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="BJ29" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:62">
       <x:c r="A30" s="11" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
         <x:v>75</x:v>
@@ -4678,10 +4690,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K30" s="12">
         <x:v>18</x:v>
@@ -4810,10 +4822,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC30" s="12">
         <x:v>18</x:v>
@@ -4837,12 +4849,12 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="BJ30" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:62">
       <x:c r="A31" s="11" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B31" s="12" t="s">
         <x:v>53</x:v>
@@ -4851,7 +4863,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D31" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E31" s="12" t="s">
         <x:v>49</x:v>
@@ -4863,22 +4875,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="L31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M31" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N31" s="12" t="s">
         <x:v>49</x:v>
@@ -4887,19 +4899,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="P31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q31" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="R31" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="S31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="T31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U31" s="12" t="s">
         <x:v>49</x:v>
@@ -4911,7 +4923,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="X31" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y31" s="12" t="s">
         <x:v>49</x:v>
@@ -4923,7 +4935,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AB31" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC31" s="12" t="s">
         <x:v>49</x:v>
@@ -4935,7 +4947,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AF31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AG31" s="12" t="s">
         <x:v>49</x:v>
@@ -4947,10 +4959,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AJ31" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK31" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL31" s="12" t="s">
         <x:v>49</x:v>
@@ -4959,7 +4971,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AN31" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO31" s="12" t="s">
         <x:v>49</x:v>
@@ -4971,7 +4983,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AR31" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS31" s="12" t="s">
         <x:v>49</x:v>
@@ -4983,7 +4995,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AV31" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW31" s="12" t="s">
         <x:v>49</x:v>
@@ -4995,13 +5007,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AZ31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BB31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC31" s="12">
         <x:v>19</x:v>
@@ -5016,21 +5028,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG31" s="12">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="BH31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="BI31" s="12">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="BJ31" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:62">
       <x:c r="A32" s="11" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
         <x:v>53</x:v>
@@ -5039,7 +5051,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E32" s="12" t="s">
         <x:v>49</x:v>
@@ -5051,19 +5063,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="L32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M32" s="12" t="s">
         <x:v>55</x:v>
@@ -5075,7 +5087,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="P32" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q32" s="12" t="s">
         <x:v>55</x:v>
@@ -5087,7 +5099,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="T32" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="U32" s="12" t="s">
         <x:v>55</x:v>
@@ -5099,10 +5111,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="X32" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y32" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Z32" s="12" t="s">
         <x:v>49</x:v>
@@ -5111,7 +5123,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AB32" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC32" s="12" t="s">
         <x:v>55</x:v>
@@ -5126,7 +5138,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AG32" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AH32" s="12" t="s">
         <x:v>49</x:v>
@@ -5135,10 +5147,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AJ32" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK32" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AL32" s="12" t="s">
         <x:v>49</x:v>
@@ -5147,19 +5159,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AN32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO32" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="AP32" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AQ32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AR32" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS32" s="12" t="s">
         <x:v>54</x:v>
@@ -5183,42 +5195,42 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AZ32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BB32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="BD32" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="BE32" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="BE32" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="BF32" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG32" s="12">
-        <x:v>32</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="BH32" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BI32" s="12">
-        <x:v>57</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="BJ32" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:62">
       <x:c r="A33" s="11" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B33" s="12" t="s">
         <x:v>53</x:v>
@@ -5227,7 +5239,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D33" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E33" s="12" t="s">
         <x:v>49</x:v>
@@ -5239,22 +5251,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="L33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M33" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N33" s="12" t="s">
         <x:v>49</x:v>
@@ -5263,7 +5275,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="P33" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q33" s="12" t="s">
         <x:v>55</x:v>
@@ -5275,7 +5287,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="T33" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U33" s="12" t="s">
         <x:v>49</x:v>
@@ -5287,10 +5299,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="X33" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z33" s="12" t="s">
         <x:v>49</x:v>
@@ -5299,7 +5311,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AB33" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC33" s="12" t="s">
         <x:v>49</x:v>
@@ -5314,7 +5326,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AG33" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AH33" s="12" t="s">
         <x:v>49</x:v>
@@ -5323,10 +5335,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AJ33" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AK33" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AL33" s="12" t="s">
         <x:v>49</x:v>
@@ -5335,22 +5347,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AN33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO33" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AP33" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AQ33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="AR33" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT33" s="12" t="s">
         <x:v>49</x:v>
@@ -5362,7 +5374,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AW33" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AX33" s="12" t="s">
         <x:v>49</x:v>
@@ -5371,19 +5383,19 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AZ33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BB33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="BD33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE33" s="12" t="s">
         <x:v>55</x:v>
@@ -5392,21 +5404,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG33" s="12">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="BH33" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="BI33" s="12">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BJ33" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:62">
       <x:c r="A34" s="11" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
         <x:v>47</x:v>
@@ -5430,10 +5442,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K34" s="12">
         <x:v>22</x:v>
@@ -5562,10 +5574,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC34" s="12">
         <x:v>22</x:v>
@@ -5589,12 +5601,12 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="BJ34" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:62">
       <x:c r="A35" s="11" t="s">
-        <x:v>113</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B35" s="12" t="s">
         <x:v>75</x:v>
@@ -5618,10 +5630,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K35" s="12">
         <x:v>23</x:v>
@@ -5750,10 +5762,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC35" s="12">
         <x:v>23</x:v>
@@ -5777,12 +5789,12 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="BJ35" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:62">
       <x:c r="A36" s="11" t="s">
-        <x:v>114</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B36" s="12" t="s">
         <x:v>75</x:v>
@@ -5806,10 +5818,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K36" s="12">
         <x:v>24</x:v>
@@ -5938,10 +5950,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC36" s="12">
         <x:v>24</x:v>
@@ -5965,12 +5977,12 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="BJ36" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:62">
       <x:c r="A37" s="11" t="s">
-        <x:v>115</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B37" s="12" t="s">
         <x:v>53</x:v>
@@ -5982,7 +5994,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F37" s="12" t="s">
         <x:v>49</x:v>
@@ -5991,13 +6003,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="H37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K37" s="12">
         <x:v>25</x:v>
@@ -6027,10 +6039,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="T37" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="U37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V37" s="12" t="s">
         <x:v>49</x:v>
@@ -6051,7 +6063,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AB37" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC37" s="12" t="s">
         <x:v>49</x:v>
@@ -6075,10 +6087,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AJ37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK37" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AL37" s="12" t="s">
         <x:v>49</x:v>
@@ -6093,16 +6105,16 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AP37" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AQ37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="AR37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AT37" s="12" t="s">
         <x:v>49</x:v>
@@ -6123,19 +6135,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AZ37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BB37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="BD37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BE37" s="12" t="s">
         <x:v>55</x:v>
@@ -6144,21 +6156,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG37" s="12">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="BH37" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="BI37" s="12">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="BJ37" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:62">
       <x:c r="A38" s="11" t="s">
-        <x:v>116</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
         <x:v>53</x:v>
@@ -6167,7 +6179,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D38" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E38" s="12" t="s">
         <x:v>54</x:v>
@@ -6179,13 +6191,13 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="H38" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I38" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J38" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K38" s="12">
         <x:v>26</x:v>
@@ -6194,7 +6206,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="M38" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N38" s="12" t="s">
         <x:v>49</x:v>
@@ -6215,10 +6227,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="T38" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U38" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V38" s="12" t="s">
         <x:v>49</x:v>
@@ -6227,7 +6239,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="X38" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y38" s="12" t="s">
         <x:v>55</x:v>
@@ -6239,10 +6251,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AB38" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC38" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD38" s="12" t="s">
         <x:v>49</x:v>
@@ -6251,10 +6263,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AF38" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG38" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH38" s="12" t="s">
         <x:v>49</x:v>
@@ -6263,7 +6275,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AJ38" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AK38" s="12" t="s">
         <x:v>64</x:v>
@@ -6275,7 +6287,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AN38" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AO38" s="12" t="s">
         <x:v>55</x:v>
@@ -6287,10 +6299,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AR38" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS38" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AT38" s="12" t="s">
         <x:v>49</x:v>
@@ -6299,7 +6311,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AV38" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AW38" s="12" t="s">
         <x:v>55</x:v>
@@ -6311,19 +6323,19 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AZ38" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA38" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BB38" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="BD38" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BE38" s="12" t="s">
         <x:v>55</x:v>
@@ -6332,21 +6344,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG38" s="12">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="BH38" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="BI38" s="12">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="BJ38" s="12" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="BI38" s="12">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="BJ38" s="12" t="s">
-        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:62">
       <x:c r="A39" s="11" t="s">
-        <x:v>117</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
         <x:v>53</x:v>
@@ -6355,10 +6367,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F39" s="12" t="s">
         <x:v>49</x:v>
@@ -6367,22 +6379,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="H39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="L39" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M39" s="12" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="M39" s="12" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="N39" s="12" t="s">
         <x:v>49</x:v>
@@ -6394,7 +6406,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="Q39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="R39" s="12" t="s">
         <x:v>49</x:v>
@@ -6403,10 +6415,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="T39" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U39" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V39" s="12" t="s">
         <x:v>49</x:v>
@@ -6415,10 +6427,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="X39" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Y39" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Z39" s="12" t="s">
         <x:v>49</x:v>
@@ -6427,10 +6439,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AB39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC39" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AD39" s="12" t="s">
         <x:v>49</x:v>
@@ -6439,10 +6451,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AF39" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AG39" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="AH39" s="12" t="s">
         <x:v>49</x:v>
@@ -6451,10 +6463,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AJ39" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AK39" s="12" t="s">
-        <x:v>119</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="AL39" s="12" t="s">
         <x:v>49</x:v>
@@ -6475,10 +6487,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AR39" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS39" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT39" s="12" t="s">
         <x:v>49</x:v>
@@ -6487,10 +6499,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AV39" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="AW39" s="12" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="AW39" s="12" t="s">
-        <x:v>63</x:v>
       </x:c>
       <x:c r="AX39" s="12" t="s">
         <x:v>49</x:v>
@@ -6499,42 +6511,42 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AZ39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BA39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="BD39" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BF39" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG39" s="12">
-        <x:v>111</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="BH39" s="12" t="s">
-        <x:v>120</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="BI39" s="12">
-        <x:v>185</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="BJ39" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:62">
       <x:c r="A40" s="11" t="s">
-        <x:v>122</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B40" s="12" t="s">
         <x:v>53</x:v>
@@ -6555,22 +6567,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="H40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="L40" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M40" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N40" s="12" t="s">
         <x:v>49</x:v>
@@ -6582,10 +6594,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="Q40" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="R40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="S40" s="12">
         <x:v>28</x:v>
@@ -6594,7 +6606,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="U40" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="V40" s="12" t="s">
         <x:v>49</x:v>
@@ -6603,10 +6615,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="X40" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Y40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z40" s="12" t="s">
         <x:v>49</x:v>
@@ -6639,10 +6651,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AJ40" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL40" s="12" t="s">
         <x:v>49</x:v>
@@ -6651,13 +6663,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AN40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO40" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="AP40" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AQ40" s="12">
         <x:v>28</x:v>
@@ -6687,42 +6699,42 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AZ40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BB40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="BD40" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BE40" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BF40" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG40" s="12">
-        <x:v>41</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BH40" s="12" t="s">
-        <x:v>123</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BI40" s="12">
-        <x:v>75</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="BJ40" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:62">
       <x:c r="A41" s="11" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B41" s="12" t="s">
         <x:v>53</x:v>
@@ -6731,10 +6743,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F41" s="12" t="s">
         <x:v>49</x:v>
@@ -6743,13 +6755,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K41" s="12">
         <x:v>29</x:v>
@@ -6767,13 +6779,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="P41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q41" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="R41" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="S41" s="12">
         <x:v>29</x:v>
@@ -6803,7 +6815,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AB41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC41" s="12" t="s">
         <x:v>55</x:v>
@@ -6827,10 +6839,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AJ41" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK41" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL41" s="12" t="s">
         <x:v>49</x:v>
@@ -6839,10 +6851,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AN41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO41" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP41" s="12" t="s">
         <x:v>54</x:v>
@@ -6851,7 +6863,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AR41" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS41" s="12" t="s">
         <x:v>64</x:v>
@@ -6875,19 +6887,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AZ41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BB41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="BD41" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BE41" s="12" t="s">
         <x:v>55</x:v>
@@ -6896,21 +6908,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG41" s="12">
-        <x:v>41</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BH41" s="12" t="s">
-        <x:v>123</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="BI41" s="12">
-        <x:v>74</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="BJ41" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:62">
       <x:c r="A42" s="11" t="s">
-        <x:v>125</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B42" s="12" t="s">
         <x:v>53</x:v>
@@ -6931,19 +6943,19 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H42" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I42" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J42" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="L42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M42" s="12" t="s">
         <x:v>55</x:v>
@@ -6955,7 +6967,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="P42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q42" s="12" t="s">
         <x:v>55</x:v>
@@ -6967,7 +6979,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="T42" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="U42" s="12" t="s">
         <x:v>55</x:v>
@@ -6979,7 +6991,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="X42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y42" s="12" t="s">
         <x:v>55</x:v>
@@ -6991,7 +7003,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AB42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC42" s="12" t="s">
         <x:v>49</x:v>
@@ -7015,10 +7027,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AJ42" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK42" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AL42" s="12" t="s">
         <x:v>49</x:v>
@@ -7027,7 +7039,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AN42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO42" s="12" t="s">
         <x:v>55</x:v>
@@ -7039,10 +7051,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AR42" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT42" s="12" t="s">
         <x:v>49</x:v>
@@ -7051,10 +7063,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AV42" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW42" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AX42" s="12" t="s">
         <x:v>49</x:v>
@@ -7063,13 +7075,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AZ42" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BA42" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BB42" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC42" s="12">
         <x:v>30</x:v>
@@ -7084,24 +7096,24 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG42" s="12">
-        <x:v>28</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="BH42" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="BI42" s="12">
-        <x:v>42</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BJ42" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:62">
       <x:c r="A43" s="11" t="s">
-        <x:v>126</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B43" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C43" s="12">
         <x:v>31</x:v>
@@ -7122,10 +7134,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K43" s="12">
         <x:v>31</x:v>
@@ -7254,10 +7266,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC43" s="12">
         <x:v>31</x:v>
@@ -7281,12 +7293,12 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="BJ43" s="12" t="s">
-        <x:v>128</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:62">
       <x:c r="A44" s="11" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
         <x:v>53</x:v>
@@ -7307,22 +7319,22 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="L44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M44" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N44" s="12" t="s">
         <x:v>49</x:v>
@@ -7331,7 +7343,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="P44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q44" s="12" t="s">
         <x:v>49</x:v>
@@ -7343,10 +7355,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="T44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U44" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="V44" s="12" t="s">
         <x:v>49</x:v>
@@ -7370,7 +7382,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AC44" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD44" s="12" t="s">
         <x:v>49</x:v>
@@ -7379,10 +7391,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AF44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AG44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AH44" s="12" t="s">
         <x:v>49</x:v>
@@ -7403,10 +7415,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AN44" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AO44" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AP44" s="12" t="s">
         <x:v>49</x:v>
@@ -7415,10 +7427,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AR44" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT44" s="12" t="s">
         <x:v>49</x:v>
@@ -7430,7 +7442,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AW44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX44" s="12" t="s">
         <x:v>49</x:v>
@@ -7439,13 +7451,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AZ44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BB44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC44" s="12">
         <x:v>32</x:v>
@@ -7454,27 +7466,27 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BE44" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF44" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG44" s="12">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BH44" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BI44" s="12">
-        <x:v>99</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BJ44" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:62">
       <x:c r="A45" s="11" t="s">
-        <x:v>130</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B45" s="12" t="s">
         <x:v>53</x:v>
@@ -7483,7 +7495,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="D45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E45" s="12" t="s">
         <x:v>49</x:v>
@@ -7495,13 +7507,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K45" s="12">
         <x:v>33</x:v>
@@ -7531,7 +7543,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="T45" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U45" s="12" t="s">
         <x:v>49</x:v>
@@ -7543,7 +7555,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="X45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y45" s="12" t="s">
         <x:v>49</x:v>
@@ -7555,7 +7567,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AB45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC45" s="12" t="s">
         <x:v>49</x:v>
@@ -7567,7 +7579,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AF45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AG45" s="12" t="s">
         <x:v>49</x:v>
@@ -7579,7 +7591,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AJ45" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AK45" s="12" t="s">
         <x:v>49</x:v>
@@ -7591,19 +7603,19 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AN45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO45" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AP45" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AQ45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AR45" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS45" s="12" t="s">
         <x:v>55</x:v>
@@ -7615,7 +7627,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AV45" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AW45" s="12" t="s">
         <x:v>49</x:v>
@@ -7627,13 +7639,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AZ45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC45" s="12">
         <x:v>33</x:v>
@@ -7648,13 +7660,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG45" s="12">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="BH45" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="BI45" s="12">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="BJ45" s="12" t="s">
         <x:v>50</x:v>
@@ -7662,7 +7674,7 @@
     </x:row>
     <x:row r="46" spans="1:62">
       <x:c r="A46" s="11" t="s">
-        <x:v>131</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
         <x:v>75</x:v>
@@ -7686,10 +7698,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K46" s="12">
         <x:v>34</x:v>
@@ -7818,10 +7830,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC46" s="12">
         <x:v>34</x:v>
@@ -7845,12 +7857,12 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="BJ46" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:62">
       <x:c r="A47" s="11" t="s">
-        <x:v>132</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B47" s="12" t="s">
         <x:v>53</x:v>
@@ -7859,10 +7871,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D47" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E47" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F47" s="12" t="s">
         <x:v>49</x:v>
@@ -7874,19 +7886,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="L47" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M47" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N47" s="12" t="s">
         <x:v>49</x:v>
@@ -7895,10 +7907,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="P47" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q47" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="R47" s="12" t="s">
         <x:v>49</x:v>
@@ -7907,10 +7919,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="T47" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U47" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="V47" s="12" t="s">
         <x:v>49</x:v>
@@ -7919,10 +7931,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="X47" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="Y47" s="12" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="Y47" s="12" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="Z47" s="12" t="s">
         <x:v>49</x:v>
@@ -7931,10 +7943,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AB47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC47" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD47" s="12" t="s">
         <x:v>49</x:v>
@@ -7943,10 +7955,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AF47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AG47" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH47" s="12" t="s">
         <x:v>49</x:v>
@@ -7955,10 +7967,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AJ47" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AK47" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL47" s="12" t="s">
         <x:v>49</x:v>
@@ -7967,10 +7979,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AN47" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AO47" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AP47" s="12" t="s">
         <x:v>49</x:v>
@@ -7982,7 +7994,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AS47" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AT47" s="12" t="s">
         <x:v>49</x:v>
@@ -8003,42 +8015,42 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AZ47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BA47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BB47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="BD47" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE47" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF47" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG47" s="12">
-        <x:v>43</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BH47" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BI47" s="12">
-        <x:v>88</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="BJ47" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:62">
       <x:c r="A48" s="11" t="s">
-        <x:v>133</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B48" s="12" t="s">
         <x:v>53</x:v>
@@ -8059,13 +8071,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K48" s="12">
         <x:v>36</x:v>
@@ -8074,7 +8086,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="M48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N48" s="12" t="s">
         <x:v>49</x:v>
@@ -8089,16 +8101,16 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="R48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="S48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="T48" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="U48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="V48" s="12" t="s">
         <x:v>49</x:v>
@@ -8107,7 +8119,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="X48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y48" s="12" t="s">
         <x:v>55</x:v>
@@ -8119,7 +8131,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AB48" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC48" s="12" t="s">
         <x:v>49</x:v>
@@ -8143,10 +8155,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AJ48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AL48" s="12" t="s">
         <x:v>49</x:v>
@@ -8155,22 +8167,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AN48" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AP48" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AQ48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AR48" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS48" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AT48" s="12" t="s">
         <x:v>49</x:v>
@@ -8179,7 +8191,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AV48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW48" s="12" t="s">
         <x:v>55</x:v>
@@ -8191,13 +8203,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AZ48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BA48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BB48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC48" s="12">
         <x:v>36</x:v>
@@ -8206,27 +8218,27 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="BE48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BF48" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG48" s="12">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="BH48" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="BI48" s="12">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="BJ48" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:62">
       <x:c r="A49" s="11" t="s">
-        <x:v>134</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B49" s="12" t="s">
         <x:v>53</x:v>
@@ -8247,13 +8259,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="H49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K49" s="12">
         <x:v>37</x:v>
@@ -8271,7 +8283,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="P49" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Q49" s="12" t="s">
         <x:v>49</x:v>
@@ -8283,10 +8295,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="T49" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="U49" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V49" s="12" t="s">
         <x:v>49</x:v>
@@ -8295,7 +8307,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="X49" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Y49" s="12" t="s">
         <x:v>49</x:v>
@@ -8307,7 +8319,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AB49" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC49" s="12" t="s">
         <x:v>49</x:v>
@@ -8331,10 +8343,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AJ49" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK49" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AL49" s="12" t="s">
         <x:v>49</x:v>
@@ -8343,13 +8355,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AN49" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AO49" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="AP49" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AQ49" s="12">
         <x:v>37</x:v>
@@ -8367,7 +8379,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AV49" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AW49" s="12" t="s">
         <x:v>55</x:v>
@@ -8379,19 +8391,19 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AZ49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BA49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="BD49" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="BE49" s="12" t="s">
         <x:v>49</x:v>
@@ -8400,21 +8412,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG49" s="12">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="BH49" s="12" t="s">
-        <x:v>128</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="BI49" s="12">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="BJ49" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:62">
       <x:c r="A50" s="11" t="s">
-        <x:v>135</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B50" s="12" t="s">
         <x:v>75</x:v>
@@ -8438,10 +8450,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K50" s="12">
         <x:v>38</x:v>
@@ -8570,10 +8582,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC50" s="12">
         <x:v>38</x:v>
@@ -8597,12 +8609,12 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="BJ50" s="12" t="s">
-        <x:v>128</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:62">
       <x:c r="A51" s="11" t="s">
-        <x:v>136</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B51" s="12" t="s">
         <x:v>53</x:v>
@@ -8623,13 +8635,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="H51" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I51" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J51" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K51" s="12">
         <x:v>39</x:v>
@@ -8638,7 +8650,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="M51" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N51" s="12" t="s">
         <x:v>49</x:v>
@@ -8647,7 +8659,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="P51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q51" s="12" t="s">
         <x:v>55</x:v>
@@ -8659,7 +8671,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="T51" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="U51" s="12" t="s">
         <x:v>49</x:v>
@@ -8671,7 +8683,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="X51" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y51" s="12" t="s">
         <x:v>49</x:v>
@@ -8686,7 +8698,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AC51" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD51" s="12" t="s">
         <x:v>49</x:v>
@@ -8698,7 +8710,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AG51" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AH51" s="12" t="s">
         <x:v>49</x:v>
@@ -8710,7 +8722,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AK51" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL51" s="12" t="s">
         <x:v>49</x:v>
@@ -8719,7 +8731,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AN51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO51" s="12" t="s">
         <x:v>49</x:v>
@@ -8734,7 +8746,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AS51" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AT51" s="12" t="s">
         <x:v>49</x:v>
@@ -8755,19 +8767,19 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AZ51" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA51" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BB51" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC51" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="BD51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE51" s="12" t="s">
         <x:v>55</x:v>
@@ -8776,21 +8788,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG51" s="12">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="BH51" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="BI51" s="12">
-        <x:v>16</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="BJ51" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:62">
       <x:c r="A52" s="11" t="s">
-        <x:v>137</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B52" s="12" t="s">
         <x:v>47</x:v>
@@ -8814,10 +8826,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I52" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J52" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K52" s="12">
         <x:v>40</x:v>
@@ -8946,10 +8958,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA52" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB52" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC52" s="12">
         <x:v>40</x:v>
@@ -8978,7 +8990,7 @@
     </x:row>
     <x:row r="53" spans="1:62">
       <x:c r="A53" s="11" t="s">
-        <x:v>138</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B53" s="12" t="s">
         <x:v>53</x:v>
@@ -8987,7 +8999,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D53" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E53" s="12" t="s">
         <x:v>49</x:v>
@@ -8999,13 +9011,13 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H53" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I53" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J53" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K53" s="12">
         <x:v>41</x:v>
@@ -9023,7 +9035,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="P53" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q53" s="12" t="s">
         <x:v>49</x:v>
@@ -9059,7 +9071,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AB53" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC53" s="12" t="s">
         <x:v>49</x:v>
@@ -9095,7 +9107,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AN53" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO53" s="12" t="s">
         <x:v>49</x:v>
@@ -9107,7 +9119,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AR53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS53" s="12" t="s">
         <x:v>49</x:v>
@@ -9131,19 +9143,19 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AZ53" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BA53" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB53" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC53" s="12">
         <x:v>41</x:v>
       </x:c>
       <x:c r="BD53" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BE53" s="12" t="s">
         <x:v>49</x:v>
@@ -9152,13 +9164,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG53" s="12">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="BH53" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="BI53" s="12">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="BJ53" s="12" t="s">
         <x:v>51</x:v>
@@ -9166,7 +9178,7 @@
     </x:row>
     <x:row r="54" spans="1:62">
       <x:c r="A54" s="11" t="s">
-        <x:v>139</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B54" s="12" t="s">
         <x:v>53</x:v>
@@ -9175,10 +9187,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="D54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F54" s="12" t="s">
         <x:v>49</x:v>
@@ -9187,22 +9199,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H54" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I54" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J54" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="L54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M54" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N54" s="12" t="s">
         <x:v>49</x:v>
@@ -9211,7 +9223,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="P54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q54" s="12" t="s">
         <x:v>49</x:v>
@@ -9226,7 +9238,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="U54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V54" s="12" t="s">
         <x:v>49</x:v>
@@ -9235,7 +9247,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="X54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y54" s="12" t="s">
         <x:v>49</x:v>
@@ -9247,10 +9259,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AB54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC54" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD54" s="12" t="s">
         <x:v>49</x:v>
@@ -9259,7 +9271,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AF54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG54" s="12" t="s">
         <x:v>64</x:v>
@@ -9271,10 +9283,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AJ54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK54" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AL54" s="12" t="s">
         <x:v>49</x:v>
@@ -9283,19 +9295,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AN54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO54" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="AP54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AQ54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="AR54" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS54" s="12" t="s">
         <x:v>64</x:v>
@@ -9307,10 +9319,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AV54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX54" s="12" t="s">
         <x:v>49</x:v>
@@ -9319,42 +9331,42 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AZ54" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA54" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BB54" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="BD54" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="BE54" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="BE54" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="BF54" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG54" s="12">
-        <x:v>53</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="BH54" s="12" t="s">
-        <x:v>140</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BI54" s="12">
-        <x:v>105</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="BJ54" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:62">
       <x:c r="A55" s="11" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B55" s="12" t="s">
         <x:v>53</x:v>
@@ -9375,13 +9387,13 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="H55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K55" s="12">
         <x:v>43</x:v>
@@ -9411,10 +9423,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="T55" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="U55" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="V55" s="12" t="s">
         <x:v>49</x:v>
@@ -9423,7 +9435,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="X55" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y55" s="12" t="s">
         <x:v>49</x:v>
@@ -9435,10 +9447,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AB55" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC55" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD55" s="12" t="s">
         <x:v>49</x:v>
@@ -9450,7 +9462,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AG55" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AH55" s="12" t="s">
         <x:v>49</x:v>
@@ -9462,7 +9474,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AK55" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL55" s="12" t="s">
         <x:v>49</x:v>
@@ -9507,42 +9519,42 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AZ55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BB55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC55" s="12">
         <x:v>43</x:v>
       </x:c>
       <x:c r="BD55" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BE55" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BF55" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG55" s="12">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="BH55" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="BI55" s="12">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="BJ55" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:62">
       <x:c r="A56" s="11" t="s">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B56" s="12" t="s">
         <x:v>53</x:v>
@@ -9551,7 +9563,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="D56" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E56" s="12" t="s">
         <x:v>54</x:v>
@@ -9563,22 +9575,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H56" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I56" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J56" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="L56" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M56" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="N56" s="12" t="s">
         <x:v>49</x:v>
@@ -9590,7 +9602,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="Q56" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="R56" s="12" t="s">
         <x:v>49</x:v>
@@ -9599,7 +9611,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="T56" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U56" s="12" t="s">
         <x:v>54</x:v>
@@ -9611,10 +9623,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="X56" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Y56" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Z56" s="12" t="s">
         <x:v>49</x:v>
@@ -9623,10 +9635,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AB56" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC56" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AD56" s="12" t="s">
         <x:v>49</x:v>
@@ -9647,10 +9659,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AJ56" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AK56" s="12" t="s">
-        <x:v>143</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="AL56" s="12" t="s">
         <x:v>49</x:v>
@@ -9659,10 +9671,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AN56" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO56" s="12" t="s">
-        <x:v>144</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="AP56" s="12" t="s">
         <x:v>49</x:v>
@@ -9671,10 +9683,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AR56" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS56" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="AT56" s="12" t="s">
         <x:v>49</x:v>
@@ -9683,7 +9695,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AV56" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW56" s="12" t="s">
         <x:v>55</x:v>
@@ -9695,42 +9707,42 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AZ56" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BA56" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BB56" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="BD56" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE56" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF56" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG56" s="12">
-        <x:v>110</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="BH56" s="12" t="s">
-        <x:v>120</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="BI56" s="12">
-        <x:v>181</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="BJ56" s="12" t="s">
-        <x:v>146</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:62">
       <x:c r="A57" s="11" t="s">
-        <x:v>147</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B57" s="12" t="s">
         <x:v>53</x:v>
@@ -9751,22 +9763,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H57" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I57" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J57" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K57" s="12">
         <x:v>45</x:v>
       </x:c>
       <x:c r="L57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M57" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N57" s="12" t="s">
         <x:v>49</x:v>
@@ -9775,7 +9787,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="P57" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q57" s="12" t="s">
         <x:v>49</x:v>
@@ -9799,10 +9811,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="X57" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Y57" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Z57" s="12" t="s">
         <x:v>49</x:v>
@@ -9811,10 +9823,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AB57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC57" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD57" s="12" t="s">
         <x:v>49</x:v>
@@ -9826,7 +9838,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AG57" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AH57" s="12" t="s">
         <x:v>49</x:v>
@@ -9835,10 +9847,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AJ57" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AK57" s="12" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="AK57" s="12" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="AL57" s="12" t="s">
         <x:v>49</x:v>
@@ -9847,7 +9859,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AN57" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO57" s="12" t="s">
         <x:v>49</x:v>
@@ -9859,7 +9871,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AR57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS57" s="12" t="s">
         <x:v>49</x:v>
@@ -9871,7 +9883,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AV57" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW57" s="12" t="s">
         <x:v>49</x:v>
@@ -9883,42 +9895,42 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AZ57" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA57" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BB57" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC57" s="12">
         <x:v>45</x:v>
       </x:c>
       <x:c r="BD57" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BE57" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BF57" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG57" s="12">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="BH57" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI57" s="12">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="BJ57" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:62">
       <x:c r="A58" s="11" t="s">
-        <x:v>148</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B58" s="12" t="s">
         <x:v>53</x:v>
@@ -9927,10 +9939,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="D58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E58" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F58" s="12" t="s">
         <x:v>49</x:v>
@@ -9939,19 +9951,19 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H58" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I58" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J58" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K58" s="12">
         <x:v>46</x:v>
       </x:c>
       <x:c r="L58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M58" s="12" t="s">
         <x:v>55</x:v>
@@ -9963,7 +9975,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="P58" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q58" s="12" t="s">
         <x:v>55</x:v>
@@ -9978,7 +9990,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="U58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V58" s="12" t="s">
         <x:v>49</x:v>
@@ -9987,10 +9999,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="X58" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y58" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Z58" s="12" t="s">
         <x:v>49</x:v>
@@ -9999,10 +10011,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AB58" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC58" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD58" s="12" t="s">
         <x:v>49</x:v>
@@ -10011,10 +10023,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AF58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG58" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH58" s="12" t="s">
         <x:v>49</x:v>
@@ -10023,7 +10035,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AJ58" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK58" s="12" t="s">
         <x:v>64</x:v>
@@ -10035,22 +10047,22 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AN58" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO58" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP58" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AQ58" s="12">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AR58" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS58" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AT58" s="12" t="s">
         <x:v>49</x:v>
@@ -10059,7 +10071,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AV58" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW58" s="12" t="s">
         <x:v>55</x:v>
@@ -10071,19 +10083,19 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AZ58" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA58" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BB58" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC58" s="12">
         <x:v>46</x:v>
       </x:c>
       <x:c r="BD58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE58" s="12" t="s">
         <x:v>55</x:v>
@@ -10092,21 +10104,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG58" s="12">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BH58" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="BI58" s="12">
-        <x:v>84</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="BJ58" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:62">
       <x:c r="A59" s="11" t="s">
-        <x:v>149</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B59" s="12" t="s">
         <x:v>53</x:v>
@@ -10115,7 +10127,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="D59" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E59" s="12" t="s">
         <x:v>49</x:v>
@@ -10127,22 +10139,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="H59" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I59" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J59" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K59" s="12">
         <x:v>47</x:v>
       </x:c>
       <x:c r="L59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M59" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N59" s="12" t="s">
         <x:v>49</x:v>
@@ -10151,10 +10163,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="P59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q59" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="R59" s="12" t="s">
         <x:v>49</x:v>
@@ -10163,7 +10175,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="T59" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="U59" s="12" t="s">
         <x:v>55</x:v>
@@ -10175,10 +10187,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="X59" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y59" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Z59" s="12" t="s">
         <x:v>49</x:v>
@@ -10187,7 +10199,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AB59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC59" s="12" t="s">
         <x:v>55</x:v>
@@ -10202,7 +10214,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AG59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AH59" s="12" t="s">
         <x:v>49</x:v>
@@ -10211,7 +10223,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AJ59" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK59" s="12" t="s">
         <x:v>64</x:v>
@@ -10223,22 +10235,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AN59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO59" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AQ59" s="12">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AR59" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT59" s="12" t="s">
         <x:v>49</x:v>
@@ -10247,10 +10259,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AV59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW59" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AX59" s="12" t="s">
         <x:v>49</x:v>
@@ -10259,42 +10271,42 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AZ59" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BA59" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BB59" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC59" s="12">
         <x:v>47</x:v>
       </x:c>
       <x:c r="BD59" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BE59" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BF59" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG59" s="12">
-        <x:v>42</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BH59" s="12" t="s">
-        <x:v>123</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="BI59" s="12">
-        <x:v>69</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="BJ59" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:62">
       <x:c r="A60" s="11" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
         <x:v>53</x:v>
@@ -10315,13 +10327,13 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H60" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I60" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J60" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K60" s="12">
         <x:v>48</x:v>
@@ -10351,7 +10363,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="T60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U60" s="12" t="s">
         <x:v>49</x:v>
@@ -10363,44 +10375,44 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="X60" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="Y60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="Z60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AA60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AB60" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="AC60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AD60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AE60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AF60" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AG60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AH60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AI60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AJ60" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="Y60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="Z60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AA60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AB60" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="AC60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AD60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AE60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AF60" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="AG60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AH60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AI60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AJ60" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="AK60" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
@@ -10411,7 +10423,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AN60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO60" s="12" t="s">
         <x:v>49</x:v>
@@ -10423,10 +10435,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AR60" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS60" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AT60" s="12" t="s">
         <x:v>49</x:v>
@@ -10447,13 +10459,13 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AZ60" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BA60" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BB60" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC60" s="12">
         <x:v>48</x:v>
@@ -10462,27 +10474,27 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="BE60" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BF60" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG60" s="12">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="BH60" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="BI60" s="12">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="BJ60" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:62">
       <x:c r="A61" s="11" t="s">
-        <x:v>151</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B61" s="12" t="s">
         <x:v>53</x:v>
@@ -10491,10 +10503,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="D61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E61" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F61" s="12" t="s">
         <x:v>49</x:v>
@@ -10503,13 +10515,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="H61" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I61" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J61" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K61" s="12">
         <x:v>49</x:v>
@@ -10527,67 +10539,67 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="P61" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q61" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="R61" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="S61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="T61" s="12" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="U61" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="V61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="W61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="X61" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="Y61" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="Z61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AA61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AB61" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AC61" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="AD61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AE61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AF61" s="12" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="AG61" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="AH61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AI61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AJ61" s="12" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="S61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="T61" s="12" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="U61" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="V61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="W61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="X61" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="Y61" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="Z61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AA61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AB61" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="AC61" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="AD61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AE61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AF61" s="12" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="AG61" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="AH61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AI61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AJ61" s="12" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="AK61" s="12" t="s">
         <x:v>64</x:v>
@@ -10599,22 +10611,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AN61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO61" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AP61" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AQ61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AR61" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="AP61" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="AQ61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AR61" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="AS61" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AT61" s="12" t="s">
         <x:v>49</x:v>
@@ -10635,42 +10647,42 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AZ61" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA61" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BB61" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BD61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BE61" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF61" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG61" s="12">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BH61" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="BI61" s="12">
-        <x:v>58</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="BJ61" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:62">
       <x:c r="A62" s="11" t="s">
-        <x:v>152</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B62" s="12" t="s">
         <x:v>53</x:v>
@@ -10679,7 +10691,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D62" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E62" s="12" t="s">
         <x:v>49</x:v>
@@ -10691,22 +10703,22 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H62" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I62" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J62" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="L62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M62" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N62" s="12" t="s">
         <x:v>49</x:v>
@@ -10727,7 +10739,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="T62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U62" s="12" t="s">
         <x:v>55</x:v>
@@ -10739,7 +10751,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="X62" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y62" s="12" t="s">
         <x:v>55</x:v>
@@ -10751,10 +10763,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AB62" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC62" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD62" s="12" t="s">
         <x:v>49</x:v>
@@ -10763,7 +10775,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AF62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AG62" s="12" t="s">
         <x:v>64</x:v>
@@ -10775,10 +10787,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AJ62" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK62" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL62" s="12" t="s">
         <x:v>49</x:v>
@@ -10787,7 +10799,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AN62" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AO62" s="12" t="s">
         <x:v>49</x:v>
@@ -10799,7 +10811,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AR62" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS62" s="12" t="s">
         <x:v>54</x:v>
@@ -10811,10 +10823,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AV62" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW62" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX62" s="12" t="s">
         <x:v>49</x:v>
@@ -10823,45 +10835,45 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AZ62" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA62" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BB62" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="BD62" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE62" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BF62" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG62" s="12">
-        <x:v>44</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BH62" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BI62" s="12">
-        <x:v>59</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="BJ62" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:62">
       <x:c r="A63" s="11" t="s">
-        <x:v>153</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B63" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C63" s="12">
         <x:v>51</x:v>
@@ -10882,10 +10894,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K63" s="12">
         <x:v>51</x:v>
@@ -11014,10 +11026,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC63" s="12">
         <x:v>51</x:v>
@@ -11046,7 +11058,7 @@
     </x:row>
     <x:row r="64" spans="1:62">
       <x:c r="A64" s="11" t="s">
-        <x:v>154</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B64" s="12" t="s">
         <x:v>53</x:v>
@@ -11055,7 +11067,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="D64" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E64" s="12" t="s">
         <x:v>49</x:v>
@@ -11067,13 +11079,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K64" s="12">
         <x:v>52</x:v>
@@ -11091,7 +11103,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="P64" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q64" s="12" t="s">
         <x:v>55</x:v>
@@ -11103,7 +11115,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="T64" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U64" s="12" t="s">
         <x:v>49</x:v>
@@ -11115,7 +11127,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="X64" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y64" s="12" t="s">
         <x:v>55</x:v>
@@ -11127,7 +11139,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AB64" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC64" s="12" t="s">
         <x:v>49</x:v>
@@ -11142,7 +11154,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AG64" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH64" s="12" t="s">
         <x:v>49</x:v>
@@ -11154,7 +11166,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK64" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AL64" s="12" t="s">
         <x:v>49</x:v>
@@ -11163,22 +11175,22 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AN64" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO64" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AP64" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AQ64" s="12">
         <x:v>52</x:v>
       </x:c>
       <x:c r="AR64" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS64" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AT64" s="12" t="s">
         <x:v>49</x:v>
@@ -11187,7 +11199,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AV64" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW64" s="12" t="s">
         <x:v>55</x:v>
@@ -11199,13 +11211,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AZ64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BB64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC64" s="12">
         <x:v>52</x:v>
@@ -11214,27 +11226,27 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="BE64" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BF64" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG64" s="12">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="BH64" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="BI64" s="12">
-        <x:v>39</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BJ64" s="12" t="s">
-        <x:v>128</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:62">
       <x:c r="A65" s="11" t="s">
-        <x:v>155</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B65" s="12" t="s">
         <x:v>53</x:v>
@@ -11243,7 +11255,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="D65" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E65" s="12" t="s">
         <x:v>49</x:v>
@@ -11255,22 +11267,22 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="H65" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I65" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J65" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="L65" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M65" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N65" s="12" t="s">
         <x:v>49</x:v>
@@ -11279,10 +11291,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="P65" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q65" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="R65" s="12" t="s">
         <x:v>49</x:v>
@@ -11303,7 +11315,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="X65" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y65" s="12" t="s">
         <x:v>55</x:v>
@@ -11315,10 +11327,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AB65" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC65" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD65" s="12" t="s">
         <x:v>49</x:v>
@@ -11327,10 +11339,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AF65" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG65" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH65" s="12" t="s">
         <x:v>49</x:v>
@@ -11339,10 +11351,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AJ65" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK65" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AL65" s="12" t="s">
         <x:v>49</x:v>
@@ -11351,22 +11363,22 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AN65" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO65" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="AP65" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AQ65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AR65" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS65" s="12" t="s">
-        <x:v>144</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="AT65" s="12" t="s">
         <x:v>49</x:v>
@@ -11375,7 +11387,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AV65" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AW65" s="12" t="s">
         <x:v>49</x:v>
@@ -11387,42 +11399,42 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AZ65" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BA65" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BB65" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="BD65" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BE65" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BF65" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG65" s="12">
-        <x:v>39</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BH65" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BI65" s="12">
-        <x:v>57</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="BJ65" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:62">
       <x:c r="A66" s="11" t="s">
-        <x:v>156</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B66" s="12" t="s">
         <x:v>53</x:v>
@@ -11434,7 +11446,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E66" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F66" s="12" t="s">
         <x:v>49</x:v>
@@ -11443,19 +11455,19 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H66" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I66" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J66" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K66" s="12">
         <x:v>54</x:v>
       </x:c>
       <x:c r="L66" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M66" s="12" t="s">
         <x:v>49</x:v>
@@ -11467,7 +11479,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="P66" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q66" s="12" t="s">
         <x:v>49</x:v>
@@ -11479,10 +11491,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="T66" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U66" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="V66" s="12" t="s">
         <x:v>49</x:v>
@@ -11491,10 +11503,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="X66" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y66" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Z66" s="12" t="s">
         <x:v>49</x:v>
@@ -11503,10 +11515,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AB66" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC66" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD66" s="12" t="s">
         <x:v>49</x:v>
@@ -11518,7 +11530,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AG66" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AH66" s="12" t="s">
         <x:v>49</x:v>
@@ -11527,10 +11539,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AJ66" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AK66" s="12" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="AK66" s="12" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="AL66" s="12" t="s">
         <x:v>49</x:v>
@@ -11542,19 +11554,19 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AO66" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AP66" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AQ66" s="12">
         <x:v>54</x:v>
       </x:c>
       <x:c r="AR66" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS66" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AT66" s="12" t="s">
         <x:v>49</x:v>
@@ -11575,13 +11587,13 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AZ66" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BA66" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="BB66" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC66" s="12">
         <x:v>54</x:v>
@@ -11590,27 +11602,27 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BE66" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BF66" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG66" s="12">
-        <x:v>30</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BH66" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="BI66" s="12">
-        <x:v>34</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BJ66" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:62">
       <x:c r="A67" s="11" t="s">
-        <x:v>157</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B67" s="12" t="s">
         <x:v>53</x:v>
@@ -11619,7 +11631,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D67" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E67" s="12" t="s">
         <x:v>55</x:v>
@@ -11631,19 +11643,19 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="H67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K67" s="12">
         <x:v>55</x:v>
       </x:c>
       <x:c r="L67" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M67" s="12" t="s">
         <x:v>49</x:v>
@@ -11655,7 +11667,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P67" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q67" s="12" t="s">
         <x:v>49</x:v>
@@ -11667,92 +11679,92 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="T67" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="U67" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="V67" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="W67" s="12">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="X67" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="Y67" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="Z67" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AA67" s="12">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="AB67" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="AC67" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="AD67" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AE67" s="12">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="AF67" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AG67" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="U67" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="V67" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="W67" s="12">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="X67" s="12" t="s">
+      <x:c r="AH67" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AI67" s="12">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="AJ67" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="Y67" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="Z67" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AA67" s="12">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AB67" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AC67" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="AD67" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AE67" s="12">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AF67" s="12" t="s">
+      <x:c r="AK67" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="AL67" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AM67" s="12">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="AN67" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="AO67" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="AP67" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AQ67" s="12">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="AR67" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="AG67" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="AH67" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AI67" s="12">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AJ67" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="AK67" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="AL67" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AM67" s="12">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AN67" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="AO67" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AP67" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AQ67" s="12">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AR67" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="AS67" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AT67" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AU67" s="12">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="AV67" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="AT67" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AU67" s="12">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AV67" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="AW67" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
@@ -11763,19 +11775,19 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AZ67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BA67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BB67" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC67" s="12">
         <x:v>55</x:v>
       </x:c>
       <x:c r="BD67" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE67" s="12" t="s">
         <x:v>55</x:v>
@@ -11784,21 +11796,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG67" s="12">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="BH67" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="BI67" s="12">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="BJ67" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:62">
       <x:c r="A68" s="11" t="s">
-        <x:v>158</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B68" s="12" t="s">
         <x:v>53</x:v>
@@ -11807,58 +11819,58 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="D68" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E68" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G68" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H68" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="I68" s="12" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="J68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K68" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="L68" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M68" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="N68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="O68" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P68" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="F68" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G68" s="12">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H68" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="I68" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="J68" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="K68" s="12">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="L68" s="12" t="s">
+      <x:c r="Q68" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="R68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="S68" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="T68" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="M68" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="N68" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="O68" s="12">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P68" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="Q68" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="R68" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="S68" s="12">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="T68" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="U68" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="V68" s="12" t="s">
         <x:v>49</x:v>
@@ -11870,31 +11882,31 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="Y68" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="Z68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AA68" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AB68" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="AC68" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="AD68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AE68" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AF68" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="Z68" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AA68" s="12">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="AB68" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AC68" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AD68" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AE68" s="12">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="AF68" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="AG68" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AH68" s="12" t="s">
         <x:v>49</x:v>
@@ -11906,32 +11918,32 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK68" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="AL68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AM68" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AN68" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="AO68" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AP68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AQ68" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AR68" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="AS68" s="12" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="AL68" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AM68" s="12">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="AN68" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="AO68" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="AP68" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AQ68" s="12">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="AR68" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="AS68" s="12" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="AT68" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
@@ -11942,7 +11954,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AW68" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AX68" s="12" t="s">
         <x:v>49</x:v>
@@ -11951,13 +11963,13 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AZ68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BA68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB68" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC68" s="12">
         <x:v>56</x:v>
@@ -11972,105 +11984,105 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG68" s="12">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BH68" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="BI68" s="12">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BJ68" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:62">
       <x:c r="A69" s="13" t="s">
-        <x:v>159</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B69" s="13" t="s">
-        <x:v>159</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C69" s="7" t="s">
-        <x:v>160</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D69" s="7"/>
       <x:c r="E69" s="7"/>
       <x:c r="F69" s="7"/>
       <x:c r="G69" s="7" t="s">
-        <x:v>161</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H69" s="7"/>
       <x:c r="I69" s="7"/>
       <x:c r="J69" s="7"/>
       <x:c r="K69" s="7" t="s">
-        <x:v>162</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="L69" s="7"/>
       <x:c r="M69" s="7"/>
       <x:c r="N69" s="7"/>
       <x:c r="O69" s="7" t="s">
-        <x:v>163</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="P69" s="7"/>
       <x:c r="Q69" s="7"/>
       <x:c r="R69" s="7"/>
       <x:c r="S69" s="7" t="s">
-        <x:v>160</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="T69" s="7"/>
       <x:c r="U69" s="7"/>
       <x:c r="V69" s="7"/>
       <x:c r="W69" s="7" t="s">
-        <x:v>163</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="X69" s="7"/>
       <x:c r="Y69" s="7"/>
       <x:c r="Z69" s="7"/>
       <x:c r="AA69" s="7" t="s">
-        <x:v>160</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="AB69" s="7"/>
       <x:c r="AC69" s="7"/>
       <x:c r="AD69" s="7"/>
       <x:c r="AE69" s="7" t="s">
-        <x:v>164</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="AF69" s="7"/>
       <x:c r="AG69" s="7"/>
       <x:c r="AH69" s="7"/>
       <x:c r="AI69" s="7" t="s">
-        <x:v>165</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="AJ69" s="7"/>
       <x:c r="AK69" s="7"/>
       <x:c r="AL69" s="7"/>
       <x:c r="AM69" s="7" t="s">
-        <x:v>164</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="AN69" s="7"/>
       <x:c r="AO69" s="7"/>
       <x:c r="AP69" s="7"/>
       <x:c r="AQ69" s="7" t="s">
-        <x:v>166</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="AR69" s="7"/>
       <x:c r="AS69" s="7"/>
       <x:c r="AT69" s="7"/>
       <x:c r="AU69" s="7" t="s">
-        <x:v>163</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="AV69" s="7"/>
       <x:c r="AW69" s="7"/>
       <x:c r="AX69" s="7"/>
       <x:c r="AY69" s="7" t="s">
-        <x:v>161</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="AZ69" s="7"/>
       <x:c r="BA69" s="7"/>
       <x:c r="BB69" s="7"/>
       <x:c r="BC69" s="7" t="s">
-        <x:v>162</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="BD69" s="7"/>
       <x:c r="BE69" s="7"/>
@@ -12082,37 +12094,37 @@
     </x:row>
     <x:row r="71" spans="1:62">
       <x:c r="A71" s="14" t="s">
-        <x:v>167</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:62">
       <x:c r="A72" s="13" t="s">
-        <x:v>168</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:62">
       <x:c r="A73" s="13" t="s">
-        <x:v>169</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:62">
       <x:c r="A74" s="13" t="s">
-        <x:v>170</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:62">
       <x:c r="A75" s="13" t="s">
-        <x:v>171</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:62">
       <x:c r="A76" s="13" t="s">
-        <x:v>172</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:62">
       <x:c r="A77" s="13" t="s">
-        <x:v>173</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/sources/2A_Manha_2_Bimestre.xlsx
+++ b/sources/2A_Manha_2_Bimestre.xlsx
@@ -210,24 +210,24 @@
     <x:t>3</x:t>
   </x:si>
   <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
     <x:t>4</x:t>
   </x:si>
   <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
     <x:t>75%</x:t>
   </x:si>
   <x:si>
@@ -348,6 +348,15 @@
     <x:t>GUILHERME EVANGELISTA LIMA</x:t>
   </x:si>
   <x:si>
+    <x:t>76%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME FELIX RIBEIRO MONTEIRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78%</x:t>
+  </x:si>
+  <x:si>
     <x:t>GUILHERME OLIVEIRA DA SILVA</x:t>
   </x:si>
   <x:si>
@@ -432,6 +441,9 @@
     <x:t>LEONARDO DE SOUZA ARAUJO</x:t>
   </x:si>
   <x:si>
+    <x:t>LUCAS DA SILVA CREPALDI</x:t>
+  </x:si>
+  <x:si>
     <x:t>LUCAS MASSI AGUENA</x:t>
   </x:si>
   <x:si>
@@ -483,9 +495,15 @@
     <x:t>RAFAELA SANTIAGO DE MORAES</x:t>
   </x:si>
   <x:si>
+    <x:t>RAQUEL RAMOS FERREIRA SILVA</x:t>
+  </x:si>
+  <x:si>
     <x:t>RENAN ALAN DOS SANTOS</x:t>
   </x:si>
   <x:si>
+    <x:t>RENIKE WENANCYO SILVA ARAUJO</x:t>
+  </x:si>
+  <x:si>
     <x:t>TAYANE EDUARDA REIS DE LIMA RIBEIRO</x:t>
   </x:si>
   <x:si>
@@ -502,21 +520,6 @@
   </x:si>
   <x:si>
     <x:t>YRAN CHRISTYAN ALVES DO NASCIMENTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAQUEL RAMOS FERREIRA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUCAS DA SILVA CREPALDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RENIKE WENANCYO SILVA ARAUJO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME FELIX RIBEIRO MONTEIRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>78%</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> </x:t>
@@ -1638,10 +1641,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BE13" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF13" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG13" s="12">
         <x:v>0</x:v>
@@ -1727,7 +1730,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="X14" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y14" s="12" t="s">
         <x:v>59</x:v>
@@ -1754,7 +1757,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AG14" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AH14" s="12" t="s">
         <x:v>49</x:v>
@@ -1766,7 +1769,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AK14" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL14" s="12" t="s">
         <x:v>49</x:v>
@@ -1781,7 +1784,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AP14" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AQ14" s="12">
         <x:v>2</x:v>
@@ -1799,7 +1802,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AV14" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW14" s="12" t="s">
         <x:v>56</x:v>
@@ -1811,10 +1814,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AZ14" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="BA14" s="12" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="BA14" s="12" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="BB14" s="12" t="s">
         <x:v>49</x:v>
@@ -1826,10 +1829,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="BE14" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BF14" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BG14" s="12">
         <x:v>82</x:v>
@@ -1855,10 +1858,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D15" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E15" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F15" s="12" t="s">
         <x:v>49</x:v>
@@ -1870,7 +1873,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I15" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J15" s="12" t="s">
         <x:v>49</x:v>
@@ -1882,7 +1885,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="M15" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N15" s="12" t="s">
         <x:v>49</x:v>
@@ -1891,7 +1894,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="P15" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q15" s="12" t="s">
         <x:v>55</x:v>
@@ -1906,7 +1909,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="U15" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="V15" s="12" t="s">
         <x:v>49</x:v>
@@ -1915,7 +1918,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="X15" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Y15" s="12" t="s">
         <x:v>58</x:v>
@@ -1963,7 +1966,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AN15" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AO15" s="12" t="s">
         <x:v>56</x:v>
@@ -1978,7 +1981,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="AS15" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AT15" s="12" t="s">
         <x:v>49</x:v>
@@ -1987,7 +1990,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AV15" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW15" s="12" t="s">
         <x:v>55</x:v>
@@ -2002,7 +2005,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BA15" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BB15" s="12" t="s">
         <x:v>49</x:v>
@@ -2011,7 +2014,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="BD15" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BE15" s="12" t="s">
         <x:v>55</x:v>
@@ -2058,7 +2061,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I16" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J16" s="12" t="s">
         <x:v>49</x:v>
@@ -2067,7 +2070,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="L16" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M16" s="12" t="s">
         <x:v>55</x:v>
@@ -2103,10 +2106,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="X16" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y16" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Z16" s="12" t="s">
         <x:v>49</x:v>
@@ -2115,10 +2118,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AB16" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AC16" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD16" s="12" t="s">
         <x:v>49</x:v>
@@ -2142,7 +2145,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK16" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AL16" s="12" t="s">
         <x:v>49</x:v>
@@ -2154,7 +2157,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AO16" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AP16" s="12" t="s">
         <x:v>49</x:v>
@@ -2199,7 +2202,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="BD16" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BE16" s="12" t="s">
         <x:v>56</x:v>
@@ -2390,10 +2393,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BE17" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF17" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG17" s="12">
         <x:v>0</x:v>
@@ -2419,7 +2422,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D18" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E18" s="12" t="s">
         <x:v>54</x:v>
@@ -2446,7 +2449,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="M18" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N18" s="12" t="s">
         <x:v>49</x:v>
@@ -2455,7 +2458,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="P18" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q18" s="12" t="s">
         <x:v>55</x:v>
@@ -2479,10 +2482,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="X18" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Y18" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Z18" s="12" t="s">
         <x:v>49</x:v>
@@ -2518,7 +2521,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="AK18" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AL18" s="12" t="s">
         <x:v>49</x:v>
@@ -2527,7 +2530,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AN18" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO18" s="12" t="s">
         <x:v>59</x:v>
@@ -2539,7 +2542,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AR18" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AS18" s="12" t="s">
         <x:v>79</x:v>
@@ -2554,7 +2557,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AW18" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AX18" s="12" t="s">
         <x:v>49</x:v>
@@ -2578,7 +2581,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BE18" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BF18" s="12" t="s">
         <x:v>49</x:v>
@@ -2766,10 +2769,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BE19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG19" s="12">
         <x:v>0</x:v>
@@ -2795,7 +2798,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D20" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E20" s="12" t="s">
         <x:v>78</x:v>
@@ -2819,10 +2822,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="L20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M20" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N20" s="12" t="s">
         <x:v>49</x:v>
@@ -2831,10 +2834,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="P20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Q20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="R20" s="12" t="s">
         <x:v>49</x:v>
@@ -2855,10 +2858,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="X20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Y20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Z20" s="12" t="s">
         <x:v>49</x:v>
@@ -2870,7 +2873,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AC20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AD20" s="12" t="s">
         <x:v>49</x:v>
@@ -2879,7 +2882,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AF20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AG20" s="12" t="s">
         <x:v>54</x:v>
@@ -2906,7 +2909,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AO20" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AP20" s="12" t="s">
         <x:v>86</x:v>
@@ -2927,7 +2930,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AV20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AW20" s="12" t="s">
         <x:v>56</x:v>
@@ -2939,10 +2942,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AZ20" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="BA20" s="12" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="BA20" s="12" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="BB20" s="12" t="s">
         <x:v>49</x:v>
@@ -2954,7 +2957,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="BE20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BF20" s="12" t="s">
         <x:v>49</x:v>
@@ -3007,7 +3010,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="L21" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M21" s="12" t="s">
         <x:v>55</x:v>
@@ -3046,7 +3049,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="Y21" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Z21" s="12" t="s">
         <x:v>49</x:v>
@@ -3055,10 +3058,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AB21" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AC21" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD21" s="12" t="s">
         <x:v>49</x:v>
@@ -3067,7 +3070,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AF21" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AG21" s="12" t="s">
         <x:v>59</x:v>
@@ -3106,7 +3109,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="AS21" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AT21" s="12" t="s">
         <x:v>49</x:v>
@@ -3139,7 +3142,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="BD21" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BE21" s="12" t="s">
         <x:v>59</x:v>
@@ -3330,10 +3333,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BE22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG22" s="12">
         <x:v>0</x:v>
@@ -3386,7 +3389,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="M23" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N23" s="12" t="s">
         <x:v>49</x:v>
@@ -3410,7 +3413,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="U23" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="V23" s="12" t="s">
         <x:v>49</x:v>
@@ -3419,7 +3422,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="X23" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Y23" s="12" t="s">
         <x:v>55</x:v>
@@ -3443,7 +3446,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AF23" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG23" s="12" t="s">
         <x:v>55</x:v>
@@ -3473,7 +3476,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AP23" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AQ23" s="12">
         <x:v>11</x:v>
@@ -3494,7 +3497,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AW23" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AX23" s="12" t="s">
         <x:v>49</x:v>
@@ -3503,10 +3506,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AZ23" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BA23" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BB23" s="12" t="s">
         <x:v>49</x:v>
@@ -3547,10 +3550,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D24" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E24" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F24" s="12" t="s">
         <x:v>49</x:v>
@@ -3562,7 +3565,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I24" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J24" s="12" t="s">
         <x:v>49</x:v>
@@ -3574,7 +3577,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="M24" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N24" s="12" t="s">
         <x:v>49</x:v>
@@ -3595,7 +3598,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="T24" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U24" s="12" t="s">
         <x:v>55</x:v>
@@ -3622,7 +3625,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AC24" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD24" s="12" t="s">
         <x:v>49</x:v>
@@ -3631,7 +3634,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AF24" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG24" s="12" t="s">
         <x:v>59</x:v>
@@ -3643,10 +3646,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AJ24" s="12" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="AK24" s="12" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="AK24" s="12" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="AL24" s="12" t="s">
         <x:v>49</x:v>
@@ -3655,10 +3658,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AN24" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO24" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AP24" s="12" t="s">
         <x:v>59</x:v>
@@ -3667,7 +3670,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AR24" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AS24" s="12" t="s">
         <x:v>78</x:v>
@@ -3682,7 +3685,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AW24" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AX24" s="12" t="s">
         <x:v>49</x:v>
@@ -3694,7 +3697,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BA24" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BB24" s="12" t="s">
         <x:v>49</x:v>
@@ -3703,7 +3706,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="BD24" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BE24" s="12" t="s">
         <x:v>58</x:v>
@@ -3786,7 +3789,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="U25" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="V25" s="12" t="s">
         <x:v>49</x:v>
@@ -3795,7 +3798,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="X25" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Y25" s="12" t="s">
         <x:v>49</x:v>
@@ -3834,7 +3837,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AK25" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AL25" s="12" t="s">
         <x:v>49</x:v>
@@ -3843,7 +3846,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AN25" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO25" s="12" t="s">
         <x:v>55</x:v>
@@ -3882,7 +3885,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BA25" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB25" s="12" t="s">
         <x:v>49</x:v>
@@ -3894,7 +3897,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BE25" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BF25" s="12" t="s">
         <x:v>49</x:v>
@@ -3923,7 +3926,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D26" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E26" s="12" t="s">
         <x:v>55</x:v>
@@ -3938,7 +3941,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I26" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J26" s="12" t="s">
         <x:v>49</x:v>
@@ -3995,7 +3998,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AB26" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AC26" s="12" t="s">
         <x:v>49</x:v>
@@ -4010,7 +4013,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AG26" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AH26" s="12" t="s">
         <x:v>49</x:v>
@@ -4031,7 +4034,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AN26" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO26" s="12" t="s">
         <x:v>49</x:v>
@@ -4043,7 +4046,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AR26" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AS26" s="12" t="s">
         <x:v>55</x:v>
@@ -4055,10 +4058,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AV26" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AW26" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AX26" s="12" t="s">
         <x:v>49</x:v>
@@ -4079,10 +4082,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="BD26" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BE26" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BF26" s="12" t="s">
         <x:v>49</x:v>
@@ -4126,7 +4129,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="I27" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J27" s="12" t="s">
         <x:v>49</x:v>
@@ -4135,10 +4138,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L27" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M27" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N27" s="12" t="s">
         <x:v>49</x:v>
@@ -4159,7 +4162,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="T27" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="U27" s="12" t="s">
         <x:v>55</x:v>
@@ -4171,7 +4174,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="X27" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Y27" s="12" t="s">
         <x:v>49</x:v>
@@ -4183,7 +4186,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AB27" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AC27" s="12" t="s">
         <x:v>49</x:v>
@@ -4210,7 +4213,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AK27" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AL27" s="12" t="s">
         <x:v>49</x:v>
@@ -4231,10 +4234,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AR27" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AS27" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AT27" s="12" t="s">
         <x:v>49</x:v>
@@ -4243,7 +4246,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AV27" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW27" s="12" t="s">
         <x:v>55</x:v>
@@ -4258,7 +4261,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BA27" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BB27" s="12" t="s">
         <x:v>49</x:v>
@@ -4267,7 +4270,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="BD27" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BE27" s="12" t="s">
         <x:v>49</x:v>
@@ -4458,10 +4461,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BE28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG28" s="12">
         <x:v>0</x:v>
@@ -4473,12 +4476,12 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="BJ28" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:62">
       <x:c r="A29" s="11" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B29" s="12" t="s">
         <x:v>53</x:v>
@@ -4487,10 +4490,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D29" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E29" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F29" s="12" t="s">
         <x:v>49</x:v>
@@ -4499,10 +4502,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="H29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I29" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J29" s="12" t="s">
         <x:v>49</x:v>
@@ -4511,7 +4514,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="L29" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M29" s="12" t="s">
         <x:v>55</x:v>
@@ -4523,10 +4526,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P29" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Q29" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="R29" s="12" t="s">
         <x:v>49</x:v>
@@ -4535,10 +4538,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="T29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U29" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="V29" s="12" t="s">
         <x:v>49</x:v>
@@ -4547,10 +4550,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="X29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Y29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Z29" s="12" t="s">
         <x:v>49</x:v>
@@ -4559,10 +4562,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AB29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC29" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AD29" s="12" t="s">
         <x:v>49</x:v>
@@ -4571,10 +4574,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AF29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AG29" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AH29" s="12" t="s">
         <x:v>49</x:v>
@@ -4583,10 +4586,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AJ29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK29" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL29" s="12" t="s">
         <x:v>49</x:v>
@@ -4595,10 +4598,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AN29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AO29" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AP29" s="12" t="s">
         <x:v>49</x:v>
@@ -4607,10 +4610,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AR29" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="AS29" s="12" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="AS29" s="12" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="AT29" s="12" t="s">
         <x:v>49</x:v>
@@ -4619,10 +4622,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AV29" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW29" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AX29" s="12" t="s">
         <x:v>49</x:v>
@@ -4631,10 +4634,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AZ29" s="12" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="BA29" s="12" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="BA29" s="12" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="BB29" s="12" t="s">
         <x:v>49</x:v>
@@ -4643,42 +4646,42 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="BD29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BE29" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BF29" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG29" s="12">
-        <x:v>64</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BH29" s="12" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="BI29" s="12">
-        <x:v>102</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BJ29" s="12" t="s">
-        <x:v>94</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:62">
       <x:c r="A30" s="11" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F30" s="12" t="s">
         <x:v>49</x:v>
@@ -4687,10 +4690,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J30" s="12" t="s">
         <x:v>49</x:v>
@@ -4699,10 +4702,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="L30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N30" s="12" t="s">
         <x:v>49</x:v>
@@ -4711,10 +4714,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="P30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Q30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R30" s="12" t="s">
         <x:v>49</x:v>
@@ -4723,10 +4726,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="T30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="V30" s="12" t="s">
         <x:v>49</x:v>
@@ -4735,10 +4738,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="X30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Z30" s="12" t="s">
         <x:v>49</x:v>
@@ -4747,10 +4750,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AB30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD30" s="12" t="s">
         <x:v>49</x:v>
@@ -4759,10 +4762,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AF30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AH30" s="12" t="s">
         <x:v>49</x:v>
@@ -4771,10 +4774,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AJ30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL30" s="12" t="s">
         <x:v>49</x:v>
@@ -4783,10 +4786,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AN30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AO30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP30" s="12" t="s">
         <x:v>49</x:v>
@@ -4795,10 +4798,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AR30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AS30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AT30" s="12" t="s">
         <x:v>49</x:v>
@@ -4807,10 +4810,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AV30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AW30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AX30" s="12" t="s">
         <x:v>49</x:v>
@@ -4819,10 +4822,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AZ30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="BB30" s="12" t="s">
         <x:v>49</x:v>
@@ -4831,39 +4834,39 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="BD30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BE30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BF30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG30" s="12">
-        <x:v>0</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BH30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="BI30" s="12">
-        <x:v>76</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="BJ30" s="12" t="s">
-        <x:v>109</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:62">
       <x:c r="A31" s="11" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D31" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E31" s="12" t="s">
         <x:v>49</x:v>
@@ -4875,7 +4878,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I31" s="12" t="s">
         <x:v>49</x:v>
@@ -4887,10 +4890,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="L31" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M31" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N31" s="12" t="s">
         <x:v>49</x:v>
@@ -4899,19 +4902,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="P31" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R31" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="T31" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U31" s="12" t="s">
         <x:v>49</x:v>
@@ -4923,7 +4926,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="X31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y31" s="12" t="s">
         <x:v>49</x:v>
@@ -4935,7 +4938,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AB31" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC31" s="12" t="s">
         <x:v>49</x:v>
@@ -4947,7 +4950,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AF31" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG31" s="12" t="s">
         <x:v>49</x:v>
@@ -4959,10 +4962,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AJ31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK31" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL31" s="12" t="s">
         <x:v>49</x:v>
@@ -4971,19 +4974,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AN31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO31" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="AP31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="AR31" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS31" s="12" t="s">
         <x:v>49</x:v>
@@ -4995,7 +4998,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AV31" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW31" s="12" t="s">
         <x:v>49</x:v>
@@ -5007,10 +5010,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AZ31" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB31" s="12" t="s">
         <x:v>49</x:v>
@@ -5019,7 +5022,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="BD31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE31" s="12" t="s">
         <x:v>49</x:v>
@@ -5028,21 +5031,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG31" s="12">
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH31" s="12" t="s">
-        <x:v>104</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BI31" s="12">
-        <x:v>36</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BJ31" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:62">
       <x:c r="A32" s="11" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
         <x:v>53</x:v>
@@ -5051,7 +5054,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D32" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E32" s="12" t="s">
         <x:v>49</x:v>
@@ -5066,7 +5069,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J32" s="12" t="s">
         <x:v>49</x:v>
@@ -5075,10 +5078,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L32" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M32" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N32" s="12" t="s">
         <x:v>49</x:v>
@@ -5087,22 +5090,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="P32" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q32" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="R32" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="S32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="T32" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U32" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V32" s="12" t="s">
         <x:v>49</x:v>
@@ -5111,10 +5114,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="X32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y32" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z32" s="12" t="s">
         <x:v>49</x:v>
@@ -5123,10 +5126,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AB32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AC32" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD32" s="12" t="s">
         <x:v>49</x:v>
@@ -5135,10 +5138,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AF32" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AG32" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH32" s="12" t="s">
         <x:v>49</x:v>
@@ -5147,10 +5150,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AJ32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK32" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL32" s="12" t="s">
         <x:v>49</x:v>
@@ -5162,10 +5165,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AO32" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP32" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AQ32" s="12">
         <x:v>20</x:v>
@@ -5174,7 +5177,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="AS32" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT32" s="12" t="s">
         <x:v>49</x:v>
@@ -5183,10 +5186,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AV32" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW32" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX32" s="12" t="s">
         <x:v>49</x:v>
@@ -5198,7 +5201,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BA32" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BB32" s="12" t="s">
         <x:v>49</x:v>
@@ -5207,30 +5210,30 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="BD32" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BE32" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF32" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG32" s="12">
-        <x:v>46</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="BH32" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="BI32" s="12">
-        <x:v>71</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="BJ32" s="12" t="s">
-        <x:v>109</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:62">
       <x:c r="A33" s="11" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B33" s="12" t="s">
         <x:v>53</x:v>
@@ -5239,7 +5242,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E33" s="12" t="s">
         <x:v>49</x:v>
@@ -5266,7 +5269,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="M33" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N33" s="12" t="s">
         <x:v>49</x:v>
@@ -5275,22 +5278,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="P33" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Q33" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="R33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="S33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="T33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="V33" s="12" t="s">
         <x:v>49</x:v>
@@ -5299,10 +5302,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="X33" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y33" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Z33" s="12" t="s">
         <x:v>49</x:v>
@@ -5311,10 +5314,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AB33" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AD33" s="12" t="s">
         <x:v>49</x:v>
@@ -5323,10 +5326,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AF33" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG33" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AH33" s="12" t="s">
         <x:v>49</x:v>
@@ -5335,10 +5338,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AJ33" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK33" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AL33" s="12" t="s">
         <x:v>49</x:v>
@@ -5350,10 +5353,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AO33" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP33" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AQ33" s="12">
         <x:v>21</x:v>
@@ -5362,7 +5365,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="AS33" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT33" s="12" t="s">
         <x:v>49</x:v>
@@ -5371,10 +5374,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AV33" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW33" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AX33" s="12" t="s">
         <x:v>49</x:v>
@@ -5386,7 +5389,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BA33" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BB33" s="12" t="s">
         <x:v>49</x:v>
@@ -5395,39 +5398,39 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="BD33" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BE33" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF33" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG33" s="12">
-        <x:v>31</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="BH33" s="12" t="s">
-        <x:v>113</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BI33" s="12">
-        <x:v>55</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="BJ33" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:62">
       <x:c r="A34" s="11" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E34" s="12" t="s">
         <x:v>49</x:v>
@@ -5439,10 +5442,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J34" s="12" t="s">
         <x:v>49</x:v>
@@ -5451,10 +5454,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="L34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N34" s="12" t="s">
         <x:v>49</x:v>
@@ -5463,10 +5466,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="P34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Q34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R34" s="12" t="s">
         <x:v>49</x:v>
@@ -5475,7 +5478,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="T34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U34" s="12" t="s">
         <x:v>49</x:v>
@@ -5487,10 +5490,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="X34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Y34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z34" s="12" t="s">
         <x:v>49</x:v>
@@ -5499,7 +5502,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AB34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AC34" s="12" t="s">
         <x:v>49</x:v>
@@ -5511,10 +5514,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AF34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AH34" s="12" t="s">
         <x:v>49</x:v>
@@ -5523,10 +5526,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AJ34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AK34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AL34" s="12" t="s">
         <x:v>49</x:v>
@@ -5535,22 +5538,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AN34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AP34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AQ34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="AR34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT34" s="12" t="s">
         <x:v>49</x:v>
@@ -5559,10 +5562,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AV34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AX34" s="12" t="s">
         <x:v>49</x:v>
@@ -5571,10 +5574,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AZ34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BB34" s="12" t="s">
         <x:v>49</x:v>
@@ -5583,33 +5586,33 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="BD34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BF34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG34" s="12">
-        <x:v>0</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="BH34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="BI34" s="12">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BJ34" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:62">
       <x:c r="A35" s="11" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B35" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C35" s="12">
         <x:v>23</x:v>
@@ -5774,10 +5777,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BE35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG35" s="12">
         <x:v>0</x:v>
@@ -5786,15 +5789,15 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BI35" s="12">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BJ35" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:62">
       <x:c r="A36" s="11" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B36" s="12" t="s">
         <x:v>75</x:v>
@@ -5962,10 +5965,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BE36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG36" s="12">
         <x:v>0</x:v>
@@ -5974,7 +5977,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BI36" s="12">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="BJ36" s="12" t="s">
         <x:v>118</x:v>
@@ -5982,19 +5985,19 @@
     </x:row>
     <x:row r="37" spans="1:62">
       <x:c r="A37" s="11" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D37" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E37" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F37" s="12" t="s">
         <x:v>49</x:v>
@@ -6003,10 +6006,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="H37" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J37" s="12" t="s">
         <x:v>49</x:v>
@@ -6015,7 +6018,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L37" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M37" s="12" t="s">
         <x:v>49</x:v>
@@ -6027,22 +6030,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="P37" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q37" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="R37" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="T37" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U37" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V37" s="12" t="s">
         <x:v>49</x:v>
@@ -6051,7 +6054,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="X37" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y37" s="12" t="s">
         <x:v>49</x:v>
@@ -6063,7 +6066,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AB37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC37" s="12" t="s">
         <x:v>49</x:v>
@@ -6075,10 +6078,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AF37" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG37" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH37" s="12" t="s">
         <x:v>49</x:v>
@@ -6087,10 +6090,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AJ37" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL37" s="12" t="s">
         <x:v>49</x:v>
@@ -6099,22 +6102,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AN37" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO37" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="AR37" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS37" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT37" s="12" t="s">
         <x:v>49</x:v>
@@ -6123,7 +6126,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AV37" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW37" s="12" t="s">
         <x:v>49</x:v>
@@ -6135,10 +6138,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AZ37" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA37" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB37" s="12" t="s">
         <x:v>49</x:v>
@@ -6147,30 +6150,30 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="BD37" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE37" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF37" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG37" s="12">
-        <x:v>32</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH37" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BI37" s="12">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="BJ37" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:62">
       <x:c r="A38" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
         <x:v>53</x:v>
@@ -6179,10 +6182,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D38" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E38" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F38" s="12" t="s">
         <x:v>49</x:v>
@@ -6194,7 +6197,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I38" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J38" s="12" t="s">
         <x:v>49</x:v>
@@ -6203,10 +6206,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="L38" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M38" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N38" s="12" t="s">
         <x:v>49</x:v>
@@ -6215,10 +6218,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="P38" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q38" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R38" s="12" t="s">
         <x:v>55</x:v>
@@ -6227,7 +6230,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="T38" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="U38" s="12" t="s">
         <x:v>56</x:v>
@@ -6239,10 +6242,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="X38" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y38" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z38" s="12" t="s">
         <x:v>49</x:v>
@@ -6254,7 +6257,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AC38" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD38" s="12" t="s">
         <x:v>49</x:v>
@@ -6263,10 +6266,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AF38" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG38" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AH38" s="12" t="s">
         <x:v>49</x:v>
@@ -6275,10 +6278,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AJ38" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK38" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AL38" s="12" t="s">
         <x:v>49</x:v>
@@ -6287,22 +6290,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AN38" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO38" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="AP38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AQ38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="AR38" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS38" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AT38" s="12" t="s">
         <x:v>49</x:v>
@@ -6311,10 +6314,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AV38" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW38" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX38" s="12" t="s">
         <x:v>49</x:v>
@@ -6326,7 +6329,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BA38" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB38" s="12" t="s">
         <x:v>49</x:v>
@@ -6335,7 +6338,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="BD38" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BE38" s="12" t="s">
         <x:v>55</x:v>
@@ -6344,21 +6347,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG38" s="12">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="BH38" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="BI38" s="12">
-        <x:v>65</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="BJ38" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:62">
       <x:c r="A39" s="11" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
         <x:v>53</x:v>
@@ -6367,10 +6370,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D39" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E39" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F39" s="12" t="s">
         <x:v>49</x:v>
@@ -6379,10 +6382,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="H39" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I39" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J39" s="12" t="s">
         <x:v>49</x:v>
@@ -6391,10 +6394,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="L39" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N39" s="12" t="s">
         <x:v>49</x:v>
@@ -6403,19 +6406,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="P39" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q39" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R39" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="S39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="T39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U39" s="12" t="s">
         <x:v>56</x:v>
@@ -6427,10 +6430,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="X39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y39" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Z39" s="12" t="s">
         <x:v>49</x:v>
@@ -6439,10 +6442,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AB39" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC39" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD39" s="12" t="s">
         <x:v>49</x:v>
@@ -6451,10 +6454,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AF39" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AG39" s="12" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="AG39" s="12" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="AH39" s="12" t="s">
         <x:v>49</x:v>
@@ -6463,10 +6466,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AJ39" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="AK39" s="12" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="AK39" s="12" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="AL39" s="12" t="s">
         <x:v>49</x:v>
@@ -6475,10 +6478,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AN39" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AO39" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP39" s="12" t="s">
         <x:v>49</x:v>
@@ -6487,10 +6490,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AR39" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS39" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AT39" s="12" t="s">
         <x:v>49</x:v>
@@ -6499,10 +6502,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AV39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AW39" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AX39" s="12" t="s">
         <x:v>49</x:v>
@@ -6511,10 +6514,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AZ39" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA39" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BB39" s="12" t="s">
         <x:v>49</x:v>
@@ -6523,30 +6526,30 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="BD39" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BE39" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BF39" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG39" s="12">
-        <x:v>138</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="BH39" s="12" t="s">
-        <x:v>124</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BI39" s="12">
-        <x:v>212</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BJ39" s="12" t="s">
-        <x:v>125</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:62">
       <x:c r="A40" s="11" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B40" s="12" t="s">
         <x:v>53</x:v>
@@ -6555,10 +6558,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D40" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F40" s="12" t="s">
         <x:v>49</x:v>
@@ -6567,10 +6570,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="H40" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I40" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J40" s="12" t="s">
         <x:v>49</x:v>
@@ -6579,7 +6582,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="L40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M40" s="12" t="s">
         <x:v>59</x:v>
@@ -6591,22 +6594,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="P40" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q40" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="R40" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="T40" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U40" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V40" s="12" t="s">
         <x:v>49</x:v>
@@ -6615,10 +6618,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="X40" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Y40" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Z40" s="12" t="s">
         <x:v>49</x:v>
@@ -6627,10 +6630,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AB40" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AC40" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AD40" s="12" t="s">
         <x:v>49</x:v>
@@ -6639,10 +6642,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AF40" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AG40" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="AH40" s="12" t="s">
         <x:v>49</x:v>
@@ -6651,10 +6654,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AJ40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AK40" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="AL40" s="12" t="s">
         <x:v>49</x:v>
@@ -6663,22 +6666,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AN40" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO40" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP40" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="AR40" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AS40" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT40" s="12" t="s">
         <x:v>49</x:v>
@@ -6687,10 +6690,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AV40" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AW40" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AX40" s="12" t="s">
         <x:v>49</x:v>
@@ -6699,10 +6702,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AZ40" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BA40" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB40" s="12" t="s">
         <x:v>49</x:v>
@@ -6711,30 +6714,30 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="BD40" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BE40" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BF40" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG40" s="12">
-        <x:v>61</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="BH40" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="BI40" s="12">
-        <x:v>95</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="BJ40" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:62">
       <x:c r="A41" s="11" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B41" s="12" t="s">
         <x:v>53</x:v>
@@ -6743,10 +6746,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F41" s="12" t="s">
         <x:v>49</x:v>
@@ -6758,7 +6761,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J41" s="12" t="s">
         <x:v>49</x:v>
@@ -6767,10 +6770,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="L41" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M41" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N41" s="12" t="s">
         <x:v>49</x:v>
@@ -6779,22 +6782,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="P41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q41" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="R41" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="S41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="T41" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="U41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="V41" s="12" t="s">
         <x:v>49</x:v>
@@ -6803,10 +6806,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="X41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y41" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z41" s="12" t="s">
         <x:v>49</x:v>
@@ -6815,10 +6818,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AB41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD41" s="12" t="s">
         <x:v>49</x:v>
@@ -6827,10 +6830,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AF41" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH41" s="12" t="s">
         <x:v>49</x:v>
@@ -6839,10 +6842,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AJ41" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK41" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL41" s="12" t="s">
         <x:v>49</x:v>
@@ -6854,19 +6857,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AO41" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AQ41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="AR41" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS41" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT41" s="12" t="s">
         <x:v>49</x:v>
@@ -6875,7 +6878,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AV41" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW41" s="12" t="s">
         <x:v>55</x:v>
@@ -6890,7 +6893,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BA41" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BB41" s="12" t="s">
         <x:v>49</x:v>
@@ -6899,30 +6902,30 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="BD41" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BE41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BF41" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG41" s="12">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BH41" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BI41" s="12">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="BJ41" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:62">
       <x:c r="A42" s="11" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B42" s="12" t="s">
         <x:v>53</x:v>
@@ -6931,10 +6934,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D42" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F42" s="12" t="s">
         <x:v>49</x:v>
@@ -6946,7 +6949,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I42" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J42" s="12" t="s">
         <x:v>49</x:v>
@@ -6955,10 +6958,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N42" s="12" t="s">
         <x:v>49</x:v>
@@ -6970,19 +6973,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="Q42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="S42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="T42" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="U42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V42" s="12" t="s">
         <x:v>49</x:v>
@@ -6991,10 +6994,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="X42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z42" s="12" t="s">
         <x:v>49</x:v>
@@ -7006,7 +7009,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AC42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AD42" s="12" t="s">
         <x:v>49</x:v>
@@ -7015,7 +7018,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AF42" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG42" s="12" t="s">
         <x:v>55</x:v>
@@ -7027,7 +7030,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AJ42" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AK42" s="12" t="s">
         <x:v>60</x:v>
@@ -7042,19 +7045,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AO42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AQ42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="AR42" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AT42" s="12" t="s">
         <x:v>49</x:v>
@@ -7063,10 +7066,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AV42" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW42" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AX42" s="12" t="s">
         <x:v>49</x:v>
@@ -7075,10 +7078,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AZ42" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA42" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BB42" s="12" t="s">
         <x:v>49</x:v>
@@ -7087,7 +7090,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="BD42" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BE42" s="12" t="s">
         <x:v>55</x:v>
@@ -7096,30 +7099,30 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG42" s="12">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BH42" s="12" t="s">
-        <x:v>109</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="BI42" s="12">
-        <x:v>52</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="BJ42" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:62">
       <x:c r="A43" s="11" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B43" s="12" t="s">
-        <x:v>130</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="D43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E43" s="12" t="s">
         <x:v>49</x:v>
@@ -7131,10 +7134,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J43" s="12" t="s">
         <x:v>49</x:v>
@@ -7143,10 +7146,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="L43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N43" s="12" t="s">
         <x:v>49</x:v>
@@ -7155,22 +7158,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="P43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="S43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="T43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="V43" s="12" t="s">
         <x:v>49</x:v>
@@ -7179,10 +7182,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="X43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Z43" s="12" t="s">
         <x:v>49</x:v>
@@ -7191,7 +7194,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AB43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC43" s="12" t="s">
         <x:v>49</x:v>
@@ -7203,10 +7206,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AF43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AH43" s="12" t="s">
         <x:v>49</x:v>
@@ -7215,10 +7218,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AJ43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AK43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AL43" s="12" t="s">
         <x:v>49</x:v>
@@ -7227,22 +7230,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AN43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AQ43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AR43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AS43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT43" s="12" t="s">
         <x:v>49</x:v>
@@ -7251,10 +7254,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AV43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AX43" s="12" t="s">
         <x:v>49</x:v>
@@ -7263,10 +7266,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AZ43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BA43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BB43" s="12" t="s">
         <x:v>49</x:v>
@@ -7275,42 +7278,42 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="BD43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BE43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BF43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG43" s="12">
-        <x:v>0</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="BH43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BI43" s="12">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BJ43" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:62">
       <x:c r="A44" s="11" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D44" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E44" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F44" s="12" t="s">
         <x:v>49</x:v>
@@ -7319,10 +7322,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I44" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J44" s="12" t="s">
         <x:v>49</x:v>
@@ -7331,10 +7334,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="L44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M44" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N44" s="12" t="s">
         <x:v>49</x:v>
@@ -7343,7 +7346,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="P44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q44" s="12" t="s">
         <x:v>49</x:v>
@@ -7355,10 +7358,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="T44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U44" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V44" s="12" t="s">
         <x:v>49</x:v>
@@ -7367,10 +7370,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="X44" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y44" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z44" s="12" t="s">
         <x:v>49</x:v>
@@ -7379,10 +7382,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AB44" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC44" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD44" s="12" t="s">
         <x:v>49</x:v>
@@ -7391,10 +7394,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AF44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH44" s="12" t="s">
         <x:v>49</x:v>
@@ -7403,10 +7406,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AJ44" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK44" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL44" s="12" t="s">
         <x:v>49</x:v>
@@ -7415,10 +7418,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AN44" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO44" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP44" s="12" t="s">
         <x:v>49</x:v>
@@ -7427,10 +7430,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AR44" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT44" s="12" t="s">
         <x:v>49</x:v>
@@ -7439,10 +7442,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AV44" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW44" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX44" s="12" t="s">
         <x:v>49</x:v>
@@ -7451,10 +7454,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AZ44" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB44" s="12" t="s">
         <x:v>49</x:v>
@@ -7463,30 +7466,30 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="BD44" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE44" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF44" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG44" s="12">
-        <x:v>61</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH44" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BI44" s="12">
-        <x:v>112</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="BJ44" s="12" t="s">
-        <x:v>132</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:62">
       <x:c r="A45" s="11" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B45" s="12" t="s">
         <x:v>53</x:v>
@@ -7495,10 +7498,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="D45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F45" s="12" t="s">
         <x:v>49</x:v>
@@ -7510,7 +7513,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I45" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J45" s="12" t="s">
         <x:v>49</x:v>
@@ -7519,10 +7522,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="L45" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N45" s="12" t="s">
         <x:v>49</x:v>
@@ -7531,7 +7534,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="P45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q45" s="12" t="s">
         <x:v>49</x:v>
@@ -7543,10 +7546,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="T45" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="V45" s="12" t="s">
         <x:v>49</x:v>
@@ -7555,10 +7558,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="X45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Y45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Z45" s="12" t="s">
         <x:v>49</x:v>
@@ -7567,10 +7570,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AB45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD45" s="12" t="s">
         <x:v>49</x:v>
@@ -7582,7 +7585,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AG45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AH45" s="12" t="s">
         <x:v>49</x:v>
@@ -7591,10 +7594,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AJ45" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="AL45" s="12" t="s">
         <x:v>49</x:v>
@@ -7603,13 +7606,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AN45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AO45" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AP45" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ45" s="12">
         <x:v>33</x:v>
@@ -7618,7 +7621,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="AS45" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT45" s="12" t="s">
         <x:v>49</x:v>
@@ -7627,10 +7630,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AV45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX45" s="12" t="s">
         <x:v>49</x:v>
@@ -7642,7 +7645,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BA45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BB45" s="12" t="s">
         <x:v>49</x:v>
@@ -7651,39 +7654,39 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="BD45" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BE45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF45" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG45" s="12">
-        <x:v>4</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BH45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BI45" s="12">
-        <x:v>3</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BJ45" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:62">
       <x:c r="A46" s="11" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E46" s="12" t="s">
         <x:v>49</x:v>
@@ -7695,10 +7698,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I46" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J46" s="12" t="s">
         <x:v>49</x:v>
@@ -7707,7 +7710,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="L46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M46" s="12" t="s">
         <x:v>49</x:v>
@@ -7731,7 +7734,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="T46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="U46" s="12" t="s">
         <x:v>49</x:v>
@@ -7743,7 +7746,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="X46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y46" s="12" t="s">
         <x:v>49</x:v>
@@ -7755,7 +7758,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AB46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC46" s="12" t="s">
         <x:v>49</x:v>
@@ -7767,7 +7770,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AF46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AG46" s="12" t="s">
         <x:v>49</x:v>
@@ -7779,7 +7782,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AJ46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AK46" s="12" t="s">
         <x:v>49</x:v>
@@ -7791,22 +7794,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AN46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO46" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AP46" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AQ46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="AR46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS46" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AT46" s="12" t="s">
         <x:v>49</x:v>
@@ -7815,7 +7818,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AV46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AW46" s="12" t="s">
         <x:v>49</x:v>
@@ -7827,7 +7830,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AZ46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA46" s="12" t="s">
         <x:v>49</x:v>
@@ -7839,30 +7842,30 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="BD46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BE46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG46" s="12">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="BH46" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="BI46" s="12">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BJ46" s="12" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="BI46" s="12">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="BJ46" s="12" t="s">
-        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:62">
       <x:c r="A47" s="11" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B47" s="12" t="s">
         <x:v>53</x:v>
@@ -7871,10 +7874,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D47" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E47" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F47" s="12" t="s">
         <x:v>49</x:v>
@@ -7883,10 +7886,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="H47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I47" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J47" s="12" t="s">
         <x:v>49</x:v>
@@ -7898,7 +7901,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="M47" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N47" s="12" t="s">
         <x:v>49</x:v>
@@ -7907,10 +7910,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="P47" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q47" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R47" s="12" t="s">
         <x:v>49</x:v>
@@ -7919,10 +7922,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="T47" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U47" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="V47" s="12" t="s">
         <x:v>49</x:v>
@@ -7931,10 +7934,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="X47" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Y47" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Z47" s="12" t="s">
         <x:v>49</x:v>
@@ -7943,10 +7946,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AB47" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AC47" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD47" s="12" t="s">
         <x:v>49</x:v>
@@ -7955,10 +7958,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AF47" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG47" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AH47" s="12" t="s">
         <x:v>49</x:v>
@@ -7967,10 +7970,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AJ47" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AK47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AL47" s="12" t="s">
         <x:v>49</x:v>
@@ -7979,19 +7982,19 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AN47" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="AO47" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="AP47" s="12" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="AO47" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="AP47" s="12" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="AR47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS47" s="12" t="s">
         <x:v>61</x:v>
@@ -8003,10 +8006,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AV47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AW47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX47" s="12" t="s">
         <x:v>49</x:v>
@@ -8015,10 +8018,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AZ47" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BA47" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="BB47" s="12" t="s">
         <x:v>49</x:v>
@@ -8027,42 +8030,42 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="BD47" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BE47" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BF47" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG47" s="12">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BH47" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="BI47" s="12">
-        <x:v>104</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BJ47" s="12" t="s">
-        <x:v>94</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:62">
       <x:c r="A48" s="11" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="D48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E48" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F48" s="12" t="s">
         <x:v>49</x:v>
@@ -8071,10 +8074,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H48" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J48" s="12" t="s">
         <x:v>49</x:v>
@@ -8083,10 +8086,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="L48" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M48" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N48" s="12" t="s">
         <x:v>49</x:v>
@@ -8095,22 +8098,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="P48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q48" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R48" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="T48" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U48" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V48" s="12" t="s">
         <x:v>49</x:v>
@@ -8119,10 +8122,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="X48" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y48" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z48" s="12" t="s">
         <x:v>49</x:v>
@@ -8131,7 +8134,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AB48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC48" s="12" t="s">
         <x:v>49</x:v>
@@ -8143,10 +8146,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AF48" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG48" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH48" s="12" t="s">
         <x:v>49</x:v>
@@ -8155,10 +8158,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AJ48" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK48" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL48" s="12" t="s">
         <x:v>49</x:v>
@@ -8167,22 +8170,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AN48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO48" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AR48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT48" s="12" t="s">
         <x:v>49</x:v>
@@ -8191,10 +8194,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AV48" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW48" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX48" s="12" t="s">
         <x:v>49</x:v>
@@ -8203,10 +8206,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AZ48" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB48" s="12" t="s">
         <x:v>49</x:v>
@@ -8215,22 +8218,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="BD48" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE48" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF48" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG48" s="12">
-        <x:v>33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH48" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BI48" s="12">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="BJ48" s="12" t="s">
         <x:v>118</x:v>
@@ -8238,7 +8241,7 @@
     </x:row>
     <x:row r="49" spans="1:62">
       <x:c r="A49" s="11" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B49" s="12" t="s">
         <x:v>53</x:v>
@@ -8247,10 +8250,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="D49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E49" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F49" s="12" t="s">
         <x:v>49</x:v>
@@ -8259,10 +8262,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="H49" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I49" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J49" s="12" t="s">
         <x:v>49</x:v>
@@ -8271,10 +8274,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="L49" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N49" s="12" t="s">
         <x:v>49</x:v>
@@ -8283,10 +8286,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="P49" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Q49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="R49" s="12" t="s">
         <x:v>49</x:v>
@@ -8295,10 +8298,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="T49" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U49" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="V49" s="12" t="s">
         <x:v>49</x:v>
@@ -8307,10 +8310,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="X49" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Y49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Z49" s="12" t="s">
         <x:v>49</x:v>
@@ -8322,7 +8325,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AC49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD49" s="12" t="s">
         <x:v>49</x:v>
@@ -8331,10 +8334,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AF49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AG49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH49" s="12" t="s">
         <x:v>49</x:v>
@@ -8343,10 +8346,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AJ49" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AK49" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL49" s="12" t="s">
         <x:v>49</x:v>
@@ -8355,22 +8358,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AN49" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AO49" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AP49" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="AR49" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AT49" s="12" t="s">
         <x:v>49</x:v>
@@ -8379,7 +8382,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AV49" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW49" s="12" t="s">
         <x:v>55</x:v>
@@ -8391,10 +8394,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AZ49" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BA49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BB49" s="12" t="s">
         <x:v>49</x:v>
@@ -8403,42 +8406,42 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="BD49" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BE49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF49" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG49" s="12">
-        <x:v>19</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BH49" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BI49" s="12">
-        <x:v>28</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="BJ49" s="12" t="s">
-        <x:v>138</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:62">
       <x:c r="A50" s="11" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B50" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C50" s="12">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F50" s="12" t="s">
         <x:v>49</x:v>
@@ -8447,10 +8450,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="H50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J50" s="12" t="s">
         <x:v>49</x:v>
@@ -8459,10 +8462,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="L50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N50" s="12" t="s">
         <x:v>49</x:v>
@@ -8471,22 +8474,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="P50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="S50" s="12">
         <x:v>38</x:v>
       </x:c>
       <x:c r="T50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="V50" s="12" t="s">
         <x:v>49</x:v>
@@ -8495,10 +8498,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="X50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Y50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Z50" s="12" t="s">
         <x:v>49</x:v>
@@ -8507,7 +8510,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AB50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC50" s="12" t="s">
         <x:v>49</x:v>
@@ -8519,10 +8522,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AF50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AH50" s="12" t="s">
         <x:v>49</x:v>
@@ -8531,10 +8534,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AJ50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AK50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AL50" s="12" t="s">
         <x:v>49</x:v>
@@ -8543,22 +8546,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AN50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AP50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AQ50" s="12">
         <x:v>38</x:v>
       </x:c>
       <x:c r="AR50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AT50" s="12" t="s">
         <x:v>49</x:v>
@@ -8567,10 +8570,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AV50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AX50" s="12" t="s">
         <x:v>49</x:v>
@@ -8579,10 +8582,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AZ50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BA50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BB50" s="12" t="s">
         <x:v>49</x:v>
@@ -8591,30 +8594,30 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="BD50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BF50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG50" s="12">
-        <x:v>0</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="BH50" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="BI50" s="12">
         <x:v>38</x:v>
       </x:c>
       <x:c r="BJ50" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:62">
       <x:c r="A51" s="11" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B51" s="12" t="s">
         <x:v>53</x:v>
@@ -8626,7 +8629,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="E51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F51" s="12" t="s">
         <x:v>49</x:v>
@@ -8638,7 +8641,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I51" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J51" s="12" t="s">
         <x:v>49</x:v>
@@ -8647,10 +8650,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="L51" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M51" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N51" s="12" t="s">
         <x:v>49</x:v>
@@ -8659,22 +8662,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="P51" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q51" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R51" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S51" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="T51" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V51" s="12" t="s">
         <x:v>49</x:v>
@@ -8683,7 +8686,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="X51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y51" s="12" t="s">
         <x:v>49</x:v>
@@ -8695,10 +8698,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AB51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC51" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD51" s="12" t="s">
         <x:v>49</x:v>
@@ -8710,7 +8713,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AG51" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH51" s="12" t="s">
         <x:v>49</x:v>
@@ -8719,10 +8722,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AJ51" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK51" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AL51" s="12" t="s">
         <x:v>49</x:v>
@@ -8731,22 +8734,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AN51" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AO51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AQ51" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="AR51" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS51" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT51" s="12" t="s">
         <x:v>49</x:v>
@@ -8755,10 +8758,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AV51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AX51" s="12" t="s">
         <x:v>49</x:v>
@@ -8767,10 +8770,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AZ51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BA51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB51" s="12" t="s">
         <x:v>49</x:v>
@@ -8779,33 +8782,33 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="BD51" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="BE51" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF51" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG51" s="12">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="BH51" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="BI51" s="12">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="BJ51" s="12" t="s">
-        <x:v>138</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:62">
       <x:c r="A52" s="11" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C52" s="12">
         <x:v>40</x:v>
@@ -8970,10 +8973,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BE52" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF52" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG52" s="12">
         <x:v>0</x:v>
@@ -8982,15 +8985,15 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BI52" s="12">
-        <x:v>3</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="BJ52" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:62">
       <x:c r="A53" s="11" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B53" s="12" t="s">
         <x:v>53</x:v>
@@ -8999,7 +9002,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D53" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E53" s="12" t="s">
         <x:v>49</x:v>
@@ -9011,10 +9014,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H53" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I53" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J53" s="12" t="s">
         <x:v>49</x:v>
@@ -9023,10 +9026,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="L53" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N53" s="12" t="s">
         <x:v>49</x:v>
@@ -9038,16 +9041,16 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="Q53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="S53" s="12">
         <x:v>41</x:v>
       </x:c>
       <x:c r="T53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U53" s="12" t="s">
         <x:v>49</x:v>
@@ -9059,7 +9062,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="X53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y53" s="12" t="s">
         <x:v>49</x:v>
@@ -9071,10 +9074,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AB53" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD53" s="12" t="s">
         <x:v>49</x:v>
@@ -9083,10 +9086,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AF53" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AG53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AH53" s="12" t="s">
         <x:v>49</x:v>
@@ -9095,10 +9098,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AJ53" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AK53" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL53" s="12" t="s">
         <x:v>49</x:v>
@@ -9119,10 +9122,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AR53" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AT53" s="12" t="s">
         <x:v>49</x:v>
@@ -9134,7 +9137,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AW53" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX53" s="12" t="s">
         <x:v>49</x:v>
@@ -9143,10 +9146,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AZ53" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BB53" s="12" t="s">
         <x:v>49</x:v>
@@ -9155,42 +9158,42 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="BD53" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BF53" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG53" s="12">
-        <x:v>5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="BH53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="BI53" s="12">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="BJ53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:62">
       <x:c r="A54" s="11" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B54" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="D54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F54" s="12" t="s">
         <x:v>49</x:v>
@@ -9199,10 +9202,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I54" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J54" s="12" t="s">
         <x:v>49</x:v>
@@ -9211,10 +9214,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M54" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N54" s="12" t="s">
         <x:v>49</x:v>
@@ -9223,7 +9226,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="P54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q54" s="12" t="s">
         <x:v>49</x:v>
@@ -9235,10 +9238,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="T54" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V54" s="12" t="s">
         <x:v>49</x:v>
@@ -9247,7 +9250,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="X54" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y54" s="12" t="s">
         <x:v>49</x:v>
@@ -9259,10 +9262,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AB54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD54" s="12" t="s">
         <x:v>49</x:v>
@@ -9271,10 +9274,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AF54" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG54" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH54" s="12" t="s">
         <x:v>49</x:v>
@@ -9283,10 +9286,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AJ54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK54" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL54" s="12" t="s">
         <x:v>49</x:v>
@@ -9295,22 +9298,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AN54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO54" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="AR54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS54" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT54" s="12" t="s">
         <x:v>49</x:v>
@@ -9319,10 +9322,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AV54" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW54" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX54" s="12" t="s">
         <x:v>49</x:v>
@@ -9331,10 +9334,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AZ54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA54" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB54" s="12" t="s">
         <x:v>49</x:v>
@@ -9343,30 +9346,30 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="BD54" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF54" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG54" s="12">
-        <x:v>69</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH54" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BI54" s="12">
-        <x:v>121</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="BJ54" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:62">
       <x:c r="A55" s="11" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B55" s="12" t="s">
         <x:v>53</x:v>
@@ -9375,10 +9378,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="D55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E55" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F55" s="12" t="s">
         <x:v>49</x:v>
@@ -9387,10 +9390,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="H55" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I55" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J55" s="12" t="s">
         <x:v>49</x:v>
@@ -9399,7 +9402,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L55" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M55" s="12" t="s">
         <x:v>49</x:v>
@@ -9411,7 +9414,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="P55" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q55" s="12" t="s">
         <x:v>49</x:v>
@@ -9423,10 +9426,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="T55" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U55" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V55" s="12" t="s">
         <x:v>49</x:v>
@@ -9435,7 +9438,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="X55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y55" s="12" t="s">
         <x:v>49</x:v>
@@ -9447,10 +9450,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AB55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC55" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD55" s="12" t="s">
         <x:v>49</x:v>
@@ -9459,10 +9462,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AF55" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH55" s="12" t="s">
         <x:v>49</x:v>
@@ -9471,10 +9474,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AJ55" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AK55" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AL55" s="12" t="s">
         <x:v>49</x:v>
@@ -9483,22 +9486,22 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AN55" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO55" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ55" s="12">
         <x:v>43</x:v>
       </x:c>
       <x:c r="AR55" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS55" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT55" s="12" t="s">
         <x:v>49</x:v>
@@ -9519,10 +9522,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AZ55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BA55" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB55" s="12" t="s">
         <x:v>49</x:v>
@@ -9531,30 +9534,30 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="BD55" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BE55" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF55" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG55" s="12">
-        <x:v>32</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="BH55" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BI55" s="12">
-        <x:v>35</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="BJ55" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:62">
       <x:c r="A56" s="11" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B56" s="12" t="s">
         <x:v>53</x:v>
@@ -9563,10 +9566,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="D56" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E56" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F56" s="12" t="s">
         <x:v>49</x:v>
@@ -9575,10 +9578,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H56" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I56" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J56" s="12" t="s">
         <x:v>49</x:v>
@@ -9590,7 +9593,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="M56" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N56" s="12" t="s">
         <x:v>49</x:v>
@@ -9599,10 +9602,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="P56" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q56" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R56" s="12" t="s">
         <x:v>49</x:v>
@@ -9611,10 +9614,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="T56" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="U56" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V56" s="12" t="s">
         <x:v>49</x:v>
@@ -9623,10 +9626,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="X56" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Y56" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z56" s="12" t="s">
         <x:v>49</x:v>
@@ -9635,10 +9638,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AB56" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC56" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD56" s="12" t="s">
         <x:v>49</x:v>
@@ -9647,10 +9650,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AF56" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AG56" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AH56" s="12" t="s">
         <x:v>49</x:v>
@@ -9659,10 +9662,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AJ56" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK56" s="12" t="s">
-        <x:v>146</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AL56" s="12" t="s">
         <x:v>49</x:v>
@@ -9671,22 +9674,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AN56" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO56" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP56" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AQ56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="AR56" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="AS56" s="12" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="AS56" s="12" t="s">
-        <x:v>147</x:v>
       </x:c>
       <x:c r="AT56" s="12" t="s">
         <x:v>49</x:v>
@@ -9695,10 +9698,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AV56" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AW56" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX56" s="12" t="s">
         <x:v>49</x:v>
@@ -9707,10 +9710,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AZ56" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA56" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BB56" s="12" t="s">
         <x:v>49</x:v>
@@ -9719,7 +9722,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="BD56" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BE56" s="12" t="s">
         <x:v>59</x:v>
@@ -9728,21 +9731,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG56" s="12">
-        <x:v>134</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="BH56" s="12" t="s">
-        <x:v>148</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BI56" s="12">
-        <x:v>205</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="BJ56" s="12" t="s">
-        <x:v>149</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:62">
       <x:c r="A57" s="11" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B57" s="12" t="s">
         <x:v>53</x:v>
@@ -9766,7 +9769,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J57" s="12" t="s">
         <x:v>49</x:v>
@@ -9775,10 +9778,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L57" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M57" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N57" s="12" t="s">
         <x:v>49</x:v>
@@ -9787,7 +9790,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="P57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q57" s="12" t="s">
         <x:v>49</x:v>
@@ -9799,10 +9802,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="T57" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="U57" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="V57" s="12" t="s">
         <x:v>49</x:v>
@@ -9811,10 +9814,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="X57" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y57" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z57" s="12" t="s">
         <x:v>49</x:v>
@@ -9826,7 +9829,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AC57" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD57" s="12" t="s">
         <x:v>49</x:v>
@@ -9835,10 +9838,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AF57" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG57" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AH57" s="12" t="s">
         <x:v>49</x:v>
@@ -9847,10 +9850,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AJ57" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="AK57" s="12" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="AK57" s="12" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="AL57" s="12" t="s">
         <x:v>49</x:v>
@@ -9859,22 +9862,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AN57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP57" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AQ57" s="12">
         <x:v>45</x:v>
       </x:c>
       <x:c r="AR57" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AT57" s="12" t="s">
         <x:v>49</x:v>
@@ -9883,10 +9886,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AV57" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AW57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AX57" s="12" t="s">
         <x:v>49</x:v>
@@ -9898,7 +9901,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BA57" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BB57" s="12" t="s">
         <x:v>49</x:v>
@@ -9910,19 +9913,19 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="BE57" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BF57" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG57" s="12">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="BH57" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="BI57" s="12">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="BJ57" s="12" t="s">
         <x:v>101</x:v>
@@ -9930,7 +9933,7 @@
     </x:row>
     <x:row r="58" spans="1:62">
       <x:c r="A58" s="11" t="s">
-        <x:v>151</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B58" s="12" t="s">
         <x:v>53</x:v>
@@ -9939,10 +9942,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="D58" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E58" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F58" s="12" t="s">
         <x:v>49</x:v>
@@ -9951,10 +9954,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H58" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J58" s="12" t="s">
         <x:v>49</x:v>
@@ -9963,10 +9966,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="L58" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M58" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="N58" s="12" t="s">
         <x:v>49</x:v>
@@ -9975,10 +9978,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="P58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q58" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="R58" s="12" t="s">
         <x:v>49</x:v>
@@ -9987,10 +9990,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="T58" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U58" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V58" s="12" t="s">
         <x:v>49</x:v>
@@ -9999,10 +10002,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="X58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Y58" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Z58" s="12" t="s">
         <x:v>49</x:v>
@@ -10011,10 +10014,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AB58" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AC58" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AD58" s="12" t="s">
         <x:v>49</x:v>
@@ -10023,10 +10026,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AF58" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG58" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AH58" s="12" t="s">
         <x:v>49</x:v>
@@ -10035,10 +10038,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AJ58" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AK58" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="AL58" s="12" t="s">
         <x:v>49</x:v>
@@ -10047,22 +10050,22 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AN58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AO58" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="AP58" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ58" s="12">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AR58" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AS58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="AT58" s="12" t="s">
         <x:v>49</x:v>
@@ -10071,7 +10074,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AV58" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AW58" s="12" t="s">
         <x:v>55</x:v>
@@ -10083,10 +10086,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AZ58" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BA58" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BB58" s="12" t="s">
         <x:v>49</x:v>
@@ -10095,30 +10098,30 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="BD58" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BE58" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF58" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG58" s="12">
-        <x:v>52</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="BH58" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="BI58" s="12">
-        <x:v>96</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="BJ58" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:62">
       <x:c r="A59" s="11" t="s">
-        <x:v>152</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B59" s="12" t="s">
         <x:v>53</x:v>
@@ -10127,10 +10130,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="D59" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E59" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F59" s="12" t="s">
         <x:v>49</x:v>
@@ -10139,10 +10142,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="H59" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I59" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J59" s="12" t="s">
         <x:v>49</x:v>
@@ -10151,10 +10154,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="L59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M59" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N59" s="12" t="s">
         <x:v>49</x:v>
@@ -10163,10 +10166,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="P59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q59" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R59" s="12" t="s">
         <x:v>49</x:v>
@@ -10175,7 +10178,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="T59" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="U59" s="12" t="s">
         <x:v>55</x:v>
@@ -10190,7 +10193,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="Y59" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Z59" s="12" t="s">
         <x:v>49</x:v>
@@ -10202,7 +10205,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AC59" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD59" s="12" t="s">
         <x:v>49</x:v>
@@ -10211,10 +10214,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AF59" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AH59" s="12" t="s">
         <x:v>49</x:v>
@@ -10223,10 +10226,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AJ59" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AK59" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AL59" s="12" t="s">
         <x:v>49</x:v>
@@ -10238,19 +10241,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AO59" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AQ59" s="12">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AR59" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS59" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT59" s="12" t="s">
         <x:v>49</x:v>
@@ -10262,7 +10265,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AW59" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX59" s="12" t="s">
         <x:v>49</x:v>
@@ -10271,10 +10274,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AZ59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB59" s="12" t="s">
         <x:v>49</x:v>
@@ -10283,30 +10286,30 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="BD59" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BE59" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BF59" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG59" s="12">
-        <x:v>54</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="BH59" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI59" s="12">
-        <x:v>81</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="BJ59" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:62">
       <x:c r="A60" s="11" t="s">
-        <x:v>153</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
         <x:v>53</x:v>
@@ -10315,56 +10318,56 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D60" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H60" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="I60" s="12" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="J60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L60" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M60" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="N60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="O60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="P60" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="Q60" s="12" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="R60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="S60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="T60" s="12" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H60" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="I60" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="J60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="K60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L60" s="12" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="M60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="N60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="O60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="P60" s="12" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="Q60" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="R60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="S60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="T60" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="U60" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
@@ -10375,10 +10378,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="X60" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Y60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Z60" s="12" t="s">
         <x:v>49</x:v>
@@ -10390,7 +10393,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AC60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD60" s="12" t="s">
         <x:v>49</x:v>
@@ -10402,7 +10405,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AG60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH60" s="12" t="s">
         <x:v>49</x:v>
@@ -10411,10 +10414,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AJ60" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AK60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AL60" s="12" t="s">
         <x:v>49</x:v>
@@ -10423,13 +10426,13 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AN60" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AQ60" s="12">
         <x:v>48</x:v>
@@ -10438,7 +10441,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="AS60" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="AT60" s="12" t="s">
         <x:v>49</x:v>
@@ -10447,7 +10450,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AV60" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AW60" s="12" t="s">
         <x:v>49</x:v>
@@ -10459,10 +10462,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AZ60" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BA60" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BB60" s="12" t="s">
         <x:v>49</x:v>
@@ -10471,30 +10474,30 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BD60" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BE60" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BF60" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG60" s="12">
-        <x:v>10</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BH60" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="BI60" s="12">
-        <x:v>26</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="BJ60" s="12" t="s">
-        <x:v>138</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:62">
       <x:c r="A61" s="11" t="s">
-        <x:v>154</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B61" s="12" t="s">
         <x:v>53</x:v>
@@ -10503,10 +10506,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="D61" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E61" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F61" s="12" t="s">
         <x:v>49</x:v>
@@ -10518,7 +10521,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I61" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J61" s="12" t="s">
         <x:v>49</x:v>
@@ -10527,97 +10530,97 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="L61" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M61" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="N61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="O61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="P61" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="Q61" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="R61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="S61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="T61" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="U61" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="V61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="W61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="X61" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="Y61" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="Z61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AA61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AB61" s="12" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="AC61" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="AD61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AE61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AF61" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AG61" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="AH61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AI61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AJ61" s="12" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="AK61" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="AL61" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AM61" s="12">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AN61" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="AO61" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="AP61" s="12" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="M61" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="N61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="O61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="P61" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="Q61" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="R61" s="12" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="S61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="T61" s="12" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="U61" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="V61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="W61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="X61" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="Y61" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="Z61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AA61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AB61" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="AC61" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="AD61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AE61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AF61" s="12" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="AG61" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="AH61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AI61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AJ61" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="AK61" s="12" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="AL61" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AM61" s="12">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AN61" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="AO61" s="12" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="AP61" s="12" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="AQ61" s="12">
         <x:v>49</x:v>
@@ -10626,7 +10629,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="AS61" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AT61" s="12" t="s">
         <x:v>49</x:v>
@@ -10635,7 +10638,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AV61" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AW61" s="12" t="s">
         <x:v>55</x:v>
@@ -10650,7 +10653,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BA61" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BB61" s="12" t="s">
         <x:v>49</x:v>
@@ -10659,30 +10662,30 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BD61" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BE61" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BF61" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG61" s="12">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BH61" s="12" t="s">
-        <x:v>132</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="BI61" s="12">
-        <x:v>71</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="BJ61" s="12" t="s">
-        <x:v>109</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:62">
       <x:c r="A62" s="11" t="s">
-        <x:v>155</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B62" s="12" t="s">
         <x:v>53</x:v>
@@ -10691,10 +10694,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D62" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F62" s="12" t="s">
         <x:v>49</x:v>
@@ -10706,7 +10709,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I62" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J62" s="12" t="s">
         <x:v>49</x:v>
@@ -10718,7 +10721,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="M62" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N62" s="12" t="s">
         <x:v>49</x:v>
@@ -10727,7 +10730,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="P62" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q62" s="12" t="s">
         <x:v>49</x:v>
@@ -10739,7 +10742,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="T62" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="U62" s="12" t="s">
         <x:v>55</x:v>
@@ -10751,10 +10754,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="X62" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Y62" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z62" s="12" t="s">
         <x:v>49</x:v>
@@ -10763,10 +10766,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AB62" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC62" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD62" s="12" t="s">
         <x:v>49</x:v>
@@ -10775,10 +10778,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AF62" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AG62" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH62" s="12" t="s">
         <x:v>49</x:v>
@@ -10787,10 +10790,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AJ62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AK62" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AL62" s="12" t="s">
         <x:v>49</x:v>
@@ -10799,10 +10802,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AN62" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AP62" s="12" t="s">
         <x:v>49</x:v>
@@ -10814,7 +10817,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="AS62" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AT62" s="12" t="s">
         <x:v>49</x:v>
@@ -10823,10 +10826,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AV62" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AW62" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX62" s="12" t="s">
         <x:v>49</x:v>
@@ -10835,10 +10838,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AZ62" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BA62" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB62" s="12" t="s">
         <x:v>49</x:v>
@@ -10847,39 +10850,39 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BD62" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BE62" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BF62" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG62" s="12">
-        <x:v>63</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="BH62" s="12" t="s">
-        <x:v>107</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="BI62" s="12">
-        <x:v>78</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="BJ62" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:62">
       <x:c r="A63" s="11" t="s">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B63" s="12" t="s">
-        <x:v>130</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C63" s="12">
         <x:v>51</x:v>
       </x:c>
       <x:c r="D63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E63" s="12" t="s">
         <x:v>49</x:v>
@@ -10891,10 +10894,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J63" s="12" t="s">
         <x:v>49</x:v>
@@ -10903,10 +10906,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="L63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N63" s="12" t="s">
         <x:v>49</x:v>
@@ -10915,10 +10918,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="P63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="R63" s="12" t="s">
         <x:v>49</x:v>
@@ -10927,10 +10930,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="T63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="V63" s="12" t="s">
         <x:v>49</x:v>
@@ -10939,10 +10942,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="X63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Y63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Z63" s="12" t="s">
         <x:v>49</x:v>
@@ -10951,10 +10954,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AB63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AD63" s="12" t="s">
         <x:v>49</x:v>
@@ -10963,10 +10966,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AF63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AH63" s="12" t="s">
         <x:v>49</x:v>
@@ -10975,10 +10978,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AJ63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AK63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL63" s="12" t="s">
         <x:v>49</x:v>
@@ -10987,22 +10990,22 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AN63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AQ63" s="12">
         <x:v>51</x:v>
       </x:c>
       <x:c r="AR63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AS63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT63" s="12" t="s">
         <x:v>49</x:v>
@@ -11011,10 +11014,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AV63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AX63" s="12" t="s">
         <x:v>49</x:v>
@@ -11023,10 +11026,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AZ63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BA63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BB63" s="12" t="s">
         <x:v>49</x:v>
@@ -11035,30 +11038,30 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="BD63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BE63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BF63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG63" s="12">
-        <x:v>0</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BH63" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="BI63" s="12">
-        <x:v>2</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="BJ63" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:62">
       <x:c r="A64" s="11" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B64" s="12" t="s">
         <x:v>53</x:v>
@@ -11067,7 +11070,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="D64" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E64" s="12" t="s">
         <x:v>49</x:v>
@@ -11082,7 +11085,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I64" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J64" s="12" t="s">
         <x:v>49</x:v>
@@ -11091,10 +11094,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="L64" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M64" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N64" s="12" t="s">
         <x:v>49</x:v>
@@ -11103,7 +11106,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="P64" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q64" s="12" t="s">
         <x:v>55</x:v>
@@ -11127,10 +11130,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="X64" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Y64" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z64" s="12" t="s">
         <x:v>49</x:v>
@@ -11151,10 +11154,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AF64" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG64" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH64" s="12" t="s">
         <x:v>49</x:v>
@@ -11163,10 +11166,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AJ64" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AK64" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL64" s="12" t="s">
         <x:v>49</x:v>
@@ -11175,13 +11178,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AN64" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO64" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP64" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ64" s="12">
         <x:v>52</x:v>
@@ -11199,10 +11202,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AV64" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW64" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX64" s="12" t="s">
         <x:v>49</x:v>
@@ -11211,10 +11214,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AZ64" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BA64" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BB64" s="12" t="s">
         <x:v>49</x:v>
@@ -11223,30 +11226,30 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="BD64" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE64" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BF64" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG64" s="12">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="BH64" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="BI64" s="12">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="BJ64" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:62">
       <x:c r="A65" s="11" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B65" s="12" t="s">
         <x:v>53</x:v>
@@ -11258,7 +11261,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="E65" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F65" s="12" t="s">
         <x:v>49</x:v>
@@ -11270,7 +11273,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="I65" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J65" s="12" t="s">
         <x:v>49</x:v>
@@ -11279,10 +11282,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="L65" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M65" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N65" s="12" t="s">
         <x:v>49</x:v>
@@ -11291,22 +11294,22 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="P65" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q65" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R65" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="S65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="T65" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="U65" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V65" s="12" t="s">
         <x:v>49</x:v>
@@ -11315,7 +11318,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="X65" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y65" s="12" t="s">
         <x:v>55</x:v>
@@ -11327,10 +11330,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AB65" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC65" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD65" s="12" t="s">
         <x:v>49</x:v>
@@ -11339,10 +11342,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AF65" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AG65" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AH65" s="12" t="s">
         <x:v>49</x:v>
@@ -11351,10 +11354,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AJ65" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK65" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL65" s="12" t="s">
         <x:v>49</x:v>
@@ -11363,22 +11366,22 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AN65" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AO65" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AP65" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AQ65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AR65" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS65" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AT65" s="12" t="s">
         <x:v>49</x:v>
@@ -11387,10 +11390,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AV65" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AW65" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AX65" s="12" t="s">
         <x:v>49</x:v>
@@ -11399,10 +11402,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AZ65" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA65" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BB65" s="12" t="s">
         <x:v>49</x:v>
@@ -11411,30 +11414,30 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="BD65" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="BE65" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="BE65" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="BF65" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG65" s="12">
-        <x:v>65</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BH65" s="12" t="s">
-        <x:v>107</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="BI65" s="12">
-        <x:v>83</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="BJ65" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:62">
       <x:c r="A66" s="11" t="s">
-        <x:v>159</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B66" s="12" t="s">
         <x:v>53</x:v>
@@ -11443,10 +11446,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="D66" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E66" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F66" s="12" t="s">
         <x:v>49</x:v>
@@ -11455,10 +11458,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H66" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I66" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J66" s="12" t="s">
         <x:v>49</x:v>
@@ -11467,10 +11470,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="L66" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M66" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N66" s="12" t="s">
         <x:v>49</x:v>
@@ -11479,7 +11482,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="P66" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q66" s="12" t="s">
         <x:v>49</x:v>
@@ -11491,10 +11494,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="T66" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U66" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="V66" s="12" t="s">
         <x:v>49</x:v>
@@ -11503,10 +11506,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="X66" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="Y66" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Z66" s="12" t="s">
         <x:v>49</x:v>
@@ -11515,10 +11518,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AB66" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AC66" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD66" s="12" t="s">
         <x:v>49</x:v>
@@ -11527,7 +11530,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AF66" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AG66" s="12" t="s">
         <x:v>63</x:v>
@@ -11539,10 +11542,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AJ66" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK66" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL66" s="12" t="s">
         <x:v>49</x:v>
@@ -11551,13 +11554,13 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AN66" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AO66" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP66" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ66" s="12">
         <x:v>54</x:v>
@@ -11566,7 +11569,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="AS66" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT66" s="12" t="s">
         <x:v>49</x:v>
@@ -11575,10 +11578,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AV66" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AW66" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX66" s="12" t="s">
         <x:v>49</x:v>
@@ -11587,10 +11590,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AZ66" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BA66" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BB66" s="12" t="s">
         <x:v>49</x:v>
@@ -11599,42 +11602,42 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BD66" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BE66" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BF66" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG66" s="12">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BH66" s="12" t="s">
-        <x:v>94</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="BI66" s="12">
-        <x:v>53</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="BJ66" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:62">
       <x:c r="A67" s="11" t="s">
-        <x:v>160</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B67" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C67" s="12">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D67" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E67" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F67" s="12" t="s">
         <x:v>49</x:v>
@@ -11643,10 +11646,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="H67" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I67" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J67" s="12" t="s">
         <x:v>49</x:v>
@@ -11655,7 +11658,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="L67" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M67" s="12" t="s">
         <x:v>49</x:v>
@@ -11667,7 +11670,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P67" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q67" s="12" t="s">
         <x:v>49</x:v>
@@ -11679,10 +11682,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="T67" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U67" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V67" s="12" t="s">
         <x:v>49</x:v>
@@ -11691,7 +11694,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="X67" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y67" s="12" t="s">
         <x:v>49</x:v>
@@ -11703,10 +11706,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AB67" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC67" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD67" s="12" t="s">
         <x:v>49</x:v>
@@ -11715,10 +11718,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AF67" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG67" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH67" s="12" t="s">
         <x:v>49</x:v>
@@ -11727,10 +11730,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AJ67" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK67" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL67" s="12" t="s">
         <x:v>49</x:v>
@@ -11739,10 +11742,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AN67" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO67" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP67" s="12" t="s">
         <x:v>49</x:v>
@@ -11751,10 +11754,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AR67" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS67" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT67" s="12" t="s">
         <x:v>49</x:v>
@@ -11763,7 +11766,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AV67" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW67" s="12" t="s">
         <x:v>49</x:v>
@@ -11775,10 +11778,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AZ67" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA67" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB67" s="12" t="s">
         <x:v>49</x:v>
@@ -11787,30 +11790,30 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BD67" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE67" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF67" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG67" s="12">
-        <x:v>31</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH67" s="12" t="s">
-        <x:v>113</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BI67" s="12">
-        <x:v>31</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BJ67" s="12" t="s">
-        <x:v>113</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:62">
       <x:c r="A68" s="11" t="s">
-        <x:v>161</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B68" s="12" t="s">
         <x:v>53</x:v>
@@ -11819,95 +11822,95 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="D68" s="12" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G68" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H68" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="I68" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K68" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="L68" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M68" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="N68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="O68" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P68" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="Q68" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="R68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="S68" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="T68" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="U68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="V68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="W68" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="X68" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="Y68" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="Z68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AA68" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AB68" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="AC68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AD68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AE68" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AF68" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="AG68" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="E68" s="12" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F68" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G68" s="12">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H68" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="I68" s="12" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="J68" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="K68" s="12">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="L68" s="12" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="M68" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="N68" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="O68" s="12">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="P68" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="Q68" s="12" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="R68" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="S68" s="12">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="T68" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="U68" s="12" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="V68" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="W68" s="12">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="X68" s="12" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="Y68" s="12" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="Z68" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AA68" s="12">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="AB68" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AC68" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AD68" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AE68" s="12">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="AF68" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="AG68" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="AH68" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
@@ -11918,22 +11921,22 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK68" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="AL68" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AM68" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AN68" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AO68" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="AL68" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AM68" s="12">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="AN68" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="AO68" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="AP68" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AQ68" s="12">
         <x:v>56</x:v>
@@ -11942,7 +11945,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="AS68" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AT68" s="12" t="s">
         <x:v>49</x:v>
@@ -11951,10 +11954,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AV68" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW68" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AX68" s="12" t="s">
         <x:v>49</x:v>
@@ -11963,10 +11966,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AZ68" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA68" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB68" s="12" t="s">
         <x:v>49</x:v>
@@ -11975,114 +11978,114 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="BD68" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BE68" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BF68" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG68" s="12">
-        <x:v>73</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="BH68" s="12" t="s">
-        <x:v>162</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="BI68" s="12">
-        <x:v>73</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BJ68" s="12" t="s">
-        <x:v>162</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:62">
       <x:c r="A69" s="13" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B69" s="13" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C69" s="7" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D69" s="7"/>
       <x:c r="E69" s="7"/>
       <x:c r="F69" s="7"/>
       <x:c r="G69" s="7" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="H69" s="7"/>
       <x:c r="I69" s="7"/>
       <x:c r="J69" s="7"/>
       <x:c r="K69" s="7" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="L69" s="7"/>
       <x:c r="M69" s="7"/>
       <x:c r="N69" s="7"/>
       <x:c r="O69" s="7" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="P69" s="7"/>
       <x:c r="Q69" s="7"/>
       <x:c r="R69" s="7"/>
       <x:c r="S69" s="7" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="T69" s="7"/>
       <x:c r="U69" s="7"/>
       <x:c r="V69" s="7"/>
       <x:c r="W69" s="7" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="X69" s="7"/>
       <x:c r="Y69" s="7"/>
       <x:c r="Z69" s="7"/>
       <x:c r="AA69" s="7" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="AB69" s="7"/>
       <x:c r="AC69" s="7"/>
       <x:c r="AD69" s="7"/>
       <x:c r="AE69" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="AF69" s="7"/>
       <x:c r="AG69" s="7"/>
       <x:c r="AH69" s="7"/>
       <x:c r="AI69" s="7" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="AJ69" s="7"/>
       <x:c r="AK69" s="7"/>
       <x:c r="AL69" s="7"/>
       <x:c r="AM69" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="AN69" s="7"/>
       <x:c r="AO69" s="7"/>
       <x:c r="AP69" s="7"/>
       <x:c r="AQ69" s="7" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="AR69" s="7"/>
       <x:c r="AS69" s="7"/>
       <x:c r="AT69" s="7"/>
       <x:c r="AU69" s="7" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="AV69" s="7"/>
       <x:c r="AW69" s="7"/>
       <x:c r="AX69" s="7"/>
       <x:c r="AY69" s="7" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="AZ69" s="7"/>
       <x:c r="BA69" s="7"/>
       <x:c r="BB69" s="7"/>
       <x:c r="BC69" s="7" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="BD69" s="7"/>
       <x:c r="BE69" s="7"/>
@@ -12094,37 +12097,37 @@
     </x:row>
     <x:row r="71" spans="1:62">
       <x:c r="A71" s="14" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:62">
       <x:c r="A72" s="13" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:62">
       <x:c r="A73" s="13" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:62">
       <x:c r="A74" s="13" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:62">
       <x:c r="A75" s="13" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:62">
       <x:c r="A76" s="13" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:62">
       <x:c r="A77" s="13" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
